--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\SEPLAG\2022\SPLOR\DCPPN\LeiOrcamentariaAnual\LOA\bancos\SISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{917932AF-78B8-41A8-99E1-97528DA1A78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC59F453-0AA8-4909-8740-C288F309EFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="150" windowWidth="21600" windowHeight="11145"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_CATEGORIA_PESSOAL" sheetId="1" r:id="rId1"/>
@@ -40,34 +40,34 @@
     <t>1011 - ALMG</t>
   </si>
   <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVA</t>
+  </si>
+  <si>
+    <t>DIREÇÃO SUPERIOR</t>
+  </si>
+  <si>
+    <t>ESPECIALIZADA</t>
+  </si>
+  <si>
+    <t>OUTRAS</t>
+  </si>
+  <si>
+    <t>TÉCNICA</t>
+  </si>
+  <si>
+    <t>MEMBROS DE PODER</t>
+  </si>
+  <si>
+    <t>DIREÇÃO E ASSESSORAMENTO</t>
+  </si>
+  <si>
     <t>Inativo</t>
   </si>
   <si>
     <t>INATIVO CIVIL</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>TÉCNICA</t>
-  </si>
-  <si>
-    <t>ESPECIALIZADA</t>
-  </si>
-  <si>
-    <t>DIREÇÃO E ASSESSORAMENTO</t>
-  </si>
-  <si>
-    <t>OUTRAS</t>
-  </si>
-  <si>
-    <t>MEMBROS DE PODER</t>
-  </si>
-  <si>
-    <t>DIREÇÃO SUPERIOR</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIVA</t>
   </si>
   <si>
     <t>1021 - TCEMG</t>
@@ -1089,7 +1089,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1138,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>1240</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1149,13 +1149,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
       <c r="E3">
-        <v>432</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1166,10 +1166,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -1183,13 +1183,13 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
         <v>11</v>
-      </c>
-      <c r="E5">
-        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1200,13 +1200,13 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1217,10 +1217,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>77</v>
@@ -1234,13 +1234,13 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1251,13 +1251,13 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9">
-        <v>2691</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1268,10 +1268,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>580</v>
@@ -1285,13 +1285,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>254</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>359</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1319,13 +1319,13 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1336,10 +1336,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>804</v>
@@ -1353,13 +1353,13 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1370,10 +1370,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>1311</v>
@@ -1387,13 +1387,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>9260</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1404,13 +1404,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="E18">
-        <v>1056</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1421,13 +1421,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
         <v>8</v>
       </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
       <c r="E19">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1455,13 +1455,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>3724</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1478,7 +1478,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>6287</v>
+        <v>9260</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1492,10 +1492,10 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1506,10 +1506,10 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>17</v>
@@ -1523,13 +1523,13 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1540,10 +1540,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26">
         <v>95</v>
@@ -1560,10 +1560,10 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1574,13 +1574,13 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1591,13 +1591,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E29">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1608,13 +1608,13 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
         <v>8</v>
       </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
       <c r="E30">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1628,10 +1628,10 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1642,13 +1642,13 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1659,13 +1659,13 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1676,13 +1676,13 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1696,10 +1696,10 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>228</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1710,13 +1710,13 @@
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>432</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1727,13 +1727,13 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1744,13 +1744,13 @@
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1761,13 +1761,13 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39">
-        <v>340</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1784,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="E40">
-        <v>800</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1795,13 +1795,13 @@
         <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E41">
-        <v>1327</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1812,13 +1812,13 @@
         <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
       </c>
       <c r="E42">
-        <v>1256</v>
+        <v>800</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1829,13 +1829,13 @@
         <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1846,13 +1846,13 @@
         <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1863,13 +1863,13 @@
         <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="E45">
-        <v>417</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1880,13 +1880,13 @@
         <v>23</v>
       </c>
       <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
         <v>8</v>
       </c>
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
       <c r="E46">
-        <v>1075</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1903,7 +1903,7 @@
         <v>7</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1914,10 +1914,10 @@
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E48">
         <v>21</v>
@@ -1931,10 +1931,10 @@
         <v>24</v>
       </c>
       <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
         <v>8</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -1948,13 +1948,13 @@
         <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
         <v>15</v>
       </c>
       <c r="E50">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1971,7 +1971,7 @@
         <v>7</v>
       </c>
       <c r="E51">
-        <v>4524</v>
+        <v>615</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,13 +1982,13 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
       </c>
       <c r="E52">
-        <v>1249</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,13 +1999,13 @@
         <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E53">
-        <v>756</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,13 +2016,13 @@
         <v>25</v>
       </c>
       <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
         <v>8</v>
       </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
       <c r="E54">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2033,13 +2033,13 @@
         <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>756</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,13 +2050,13 @@
         <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
       </c>
       <c r="E56">
-        <v>615</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="E57">
-        <v>439</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E58">
         <v>84</v>
@@ -2101,10 +2101,10 @@
         <v>26</v>
       </c>
       <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
         <v>8</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
       </c>
       <c r="E59">
         <v>6</v>
@@ -2118,13 +2118,13 @@
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
       </c>
       <c r="E60">
-        <v>109</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2141,7 +2141,7 @@
         <v>7</v>
       </c>
       <c r="E61">
-        <v>551</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
       </c>
       <c r="E62">
-        <v>43</v>
+        <v>551</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,10 +2169,10 @@
         <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E63">
         <v>45</v>
@@ -2186,10 +2186,10 @@
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E64">
         <v>120</v>
@@ -2203,10 +2203,10 @@
         <v>27</v>
       </c>
       <c r="C65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
         <v>8</v>
-      </c>
-      <c r="D65" t="s">
-        <v>14</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -2223,10 +2223,10 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E66">
-        <v>483</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2240,10 +2240,10 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E67">
-        <v>37052</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,13 +2254,13 @@
         <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E68">
-        <v>219</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2271,13 +2271,13 @@
         <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E69">
-        <v>2248</v>
+        <v>35009</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,13 +2288,13 @@
         <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2305,13 +2305,13 @@
         <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E71">
-        <v>3477</v>
+        <v>37052</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2322,13 +2322,13 @@
         <v>28</v>
       </c>
       <c r="C72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
         <v>8</v>
       </c>
-      <c r="D72" t="s">
-        <v>31</v>
-      </c>
       <c r="E72">
-        <v>35009</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2339,13 +2339,13 @@
         <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2356,13 +2356,13 @@
         <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E74">
-        <v>257</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,13 +2373,13 @@
         <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
       </c>
       <c r="E75">
-        <v>1492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2393,10 +2393,10 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E76">
-        <v>175328</v>
+        <v>151539</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2407,13 +2407,13 @@
         <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77">
-        <v>12146</v>
+        <v>39888</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2424,13 +2424,13 @@
         <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E78">
-        <v>151539</v>
+        <v>175328</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,13 +2441,13 @@
         <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
       <c r="E79">
-        <v>22668</v>
+        <v>12146</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,13 +2458,13 @@
         <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2475,13 +2475,13 @@
         <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
       </c>
       <c r="E81">
-        <v>4256</v>
+        <v>22668</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2492,13 +2492,13 @@
         <v>32</v>
       </c>
       <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s">
         <v>8</v>
       </c>
-      <c r="D82" t="s">
-        <v>15</v>
-      </c>
       <c r="E82">
-        <v>39888</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2515,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="E83">
-        <v>290</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2526,13 +2526,13 @@
         <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E84">
-        <v>78</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2543,10 +2543,10 @@
         <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E85">
         <v>11</v>
@@ -2560,10 +2560,10 @@
         <v>33</v>
       </c>
       <c r="C86" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
         <v>8</v>
-      </c>
-      <c r="D86" t="s">
-        <v>14</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -2577,10 +2577,10 @@
         <v>33</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E87">
         <v>162</v>
@@ -2594,13 +2594,13 @@
         <v>33</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="E89">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2628,10 +2628,10 @@
         <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E90">
         <v>35</v>
@@ -2645,10 +2645,10 @@
         <v>34</v>
       </c>
       <c r="C91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
         <v>8</v>
-      </c>
-      <c r="D91" t="s">
-        <v>14</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -2662,13 +2662,13 @@
         <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
       </c>
       <c r="E92">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,10 +2679,10 @@
         <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E93">
         <v>13</v>
@@ -2696,13 +2696,13 @@
         <v>35</v>
       </c>
       <c r="C94" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s">
         <v>8</v>
       </c>
-      <c r="D94" t="s">
-        <v>10</v>
-      </c>
       <c r="E94">
-        <v>607</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2713,13 +2713,13 @@
         <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
       <c r="E95">
-        <v>128</v>
+        <v>607</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2730,13 +2730,13 @@
         <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="E96">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2747,13 +2747,13 @@
         <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E97">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2767,10 +2767,10 @@
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E98">
-        <v>2884</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2781,13 +2781,13 @@
         <v>36</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E99">
-        <v>80</v>
+        <v>863</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2798,10 +2798,10 @@
         <v>36</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E100">
         <v>23</v>
@@ -2815,13 +2815,13 @@
         <v>36</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E101">
-        <v>4895</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2832,13 +2832,13 @@
         <v>36</v>
       </c>
       <c r="C102" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E102">
-        <v>863</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="E103">
-        <v>391</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2866,13 +2866,13 @@
         <v>37</v>
       </c>
       <c r="C104" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E104">
-        <v>704</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2883,13 +2883,13 @@
         <v>37</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E105">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,13 +2900,13 @@
         <v>37</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E106">
-        <v>10</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,13 +2917,13 @@
         <v>37</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E107">
-        <v>3</v>
+        <v>704</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,13 +2934,13 @@
         <v>37</v>
       </c>
       <c r="C108" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
         <v>8</v>
       </c>
-      <c r="D108" t="s">
-        <v>10</v>
-      </c>
       <c r="E108">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2957,7 +2957,7 @@
         <v>7</v>
       </c>
       <c r="E109">
-        <v>695</v>
+        <v>928</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,13 +2968,13 @@
         <v>38</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E110">
-        <v>1241</v>
+        <v>695</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2985,13 +2985,13 @@
         <v>38</v>
       </c>
       <c r="C111" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
         <v>8</v>
       </c>
-      <c r="D111" t="s">
-        <v>15</v>
-      </c>
       <c r="E111">
-        <v>928</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,13 +3002,13 @@
         <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D112" t="s">
         <v>9</v>
       </c>
       <c r="E112">
-        <v>19919</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -3019,13 +3019,13 @@
         <v>38</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E113">
-        <v>283</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -3036,13 +3036,13 @@
         <v>38</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>19919</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -3053,13 +3053,13 @@
         <v>38</v>
       </c>
       <c r="C115" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E115">
-        <v>8</v>
+        <v>283</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -3076,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="E116">
-        <v>1240</v>
+        <v>130</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -3087,13 +3087,13 @@
         <v>39</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E117">
-        <v>186</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -3104,13 +3104,13 @@
         <v>39</v>
       </c>
       <c r="C118" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s">
         <v>8</v>
       </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
       <c r="E118">
-        <v>178</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -3121,13 +3121,13 @@
         <v>39</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E119">
-        <v>6</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -3138,13 +3138,13 @@
         <v>39</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120">
-        <v>264</v>
+        <v>178</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -3155,13 +3155,13 @@
         <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E121">
-        <v>130</v>
+        <v>186</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,10 +3175,10 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E122">
-        <v>1183</v>
+        <v>47</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3189,13 +3189,13 @@
         <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E123">
-        <v>49</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -3206,13 +3206,13 @@
         <v>40</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E124">
-        <v>47</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,10 +3223,10 @@
         <v>40</v>
       </c>
       <c r="C125" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" t="s">
         <v>8</v>
-      </c>
-      <c r="D125" t="s">
-        <v>14</v>
       </c>
       <c r="E125">
         <v>13</v>
@@ -3240,13 +3240,13 @@
         <v>40</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E126">
-        <v>234</v>
+        <v>49</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3257,10 +3257,10 @@
         <v>40</v>
       </c>
       <c r="C127" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E127">
         <v>28</v>
@@ -3277,10 +3277,10 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E128">
-        <v>1733</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,13 +3291,13 @@
         <v>41</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E129">
-        <v>528</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,13 +3308,13 @@
         <v>41</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,13 +3325,13 @@
         <v>41</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E131">
-        <v>380</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -3345,10 +3345,10 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E132">
-        <v>7385</v>
+        <v>868</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -3359,10 +3359,10 @@
         <v>42</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E133">
         <v>9678</v>
@@ -3376,13 +3376,13 @@
         <v>42</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E134">
-        <v>868</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -3393,13 +3393,13 @@
         <v>42</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s">
         <v>15</v>
       </c>
       <c r="E135">
-        <v>282</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -3410,13 +3410,13 @@
         <v>42</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E136">
-        <v>12</v>
+        <v>282</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>42</v>
       </c>
       <c r="C137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
         <v>8</v>
-      </c>
-      <c r="D137" t="s">
-        <v>14</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -3444,13 +3444,13 @@
         <v>43</v>
       </c>
       <c r="C138" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138">
         <v>15</v>
-      </c>
-      <c r="E138">
-        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -3461,13 +3461,13 @@
         <v>43</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E139">
-        <v>15</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -3478,10 +3478,10 @@
         <v>43</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E140">
         <v>17</v>
@@ -3495,13 +3495,13 @@
         <v>43</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,13 +3512,13 @@
         <v>43</v>
       </c>
       <c r="C142" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E142">
-        <v>142</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -3532,10 +3532,10 @@
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E143">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -3546,13 +3546,13 @@
         <v>44</v>
       </c>
       <c r="C144" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -3563,13 +3563,13 @@
         <v>44</v>
       </c>
       <c r="C145" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s">
         <v>8</v>
       </c>
-      <c r="D145" t="s">
-        <v>15</v>
-      </c>
       <c r="E145">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -3580,13 +3580,13 @@
         <v>44</v>
       </c>
       <c r="C146" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E146">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -3603,7 +3603,7 @@
         <v>7</v>
       </c>
       <c r="E147">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -3614,13 +3614,13 @@
         <v>44</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E148">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -3631,13 +3631,13 @@
         <v>45</v>
       </c>
       <c r="C149" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D149" t="s">
         <v>13</v>
       </c>
       <c r="E149">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -3648,10 +3648,10 @@
         <v>45</v>
       </c>
       <c r="C150" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" t="s">
         <v>8</v>
-      </c>
-      <c r="D150" t="s">
-        <v>9</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -3665,10 +3665,10 @@
         <v>45</v>
       </c>
       <c r="C151" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -3682,13 +3682,13 @@
         <v>45</v>
       </c>
       <c r="C152" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E152">
-        <v>116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -3699,10 +3699,10 @@
         <v>45</v>
       </c>
       <c r="C153" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E153">
         <v>3</v>
@@ -3716,13 +3716,13 @@
         <v>46</v>
       </c>
       <c r="C154" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D154" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E154">
-        <v>600</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="E155">
-        <v>3231</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -3750,13 +3750,13 @@
         <v>46</v>
       </c>
       <c r="C156" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E156">
-        <v>1019</v>
+        <v>600</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -3767,10 +3767,10 @@
         <v>46</v>
       </c>
       <c r="C157" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E157">
         <v>843</v>
@@ -3784,10 +3784,10 @@
         <v>46</v>
       </c>
       <c r="C158" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E158">
         <v>96</v>
@@ -3801,10 +3801,10 @@
         <v>46</v>
       </c>
       <c r="C159" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s">
         <v>8</v>
-      </c>
-      <c r="D159" t="s">
-        <v>14</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -3818,13 +3818,13 @@
         <v>47</v>
       </c>
       <c r="C160" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E160">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -3835,10 +3835,10 @@
         <v>47</v>
       </c>
       <c r="C161" t="s">
+        <v>6</v>
+      </c>
+      <c r="D161" t="s">
         <v>8</v>
-      </c>
-      <c r="D161" t="s">
-        <v>14</v>
       </c>
       <c r="E161">
         <v>3</v>
@@ -3852,10 +3852,10 @@
         <v>47</v>
       </c>
       <c r="C162" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E162">
         <v>48</v>
@@ -3869,13 +3869,13 @@
         <v>47</v>
       </c>
       <c r="C163" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -3886,10 +3886,10 @@
         <v>48</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -3903,13 +3903,13 @@
         <v>48</v>
       </c>
       <c r="C165" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s">
         <v>8</v>
       </c>
-      <c r="D165" t="s">
-        <v>9</v>
-      </c>
       <c r="E165">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -3923,10 +3923,10 @@
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E166">
-        <v>280</v>
+        <v>59</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -3937,13 +3937,13 @@
         <v>48</v>
       </c>
       <c r="C167" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D167" t="s">
         <v>11</v>
       </c>
       <c r="E167">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -3954,13 +3954,13 @@
         <v>48</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -3971,10 +3971,10 @@
         <v>48</v>
       </c>
       <c r="C169" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E169">
         <v>109</v>
@@ -3988,13 +3988,13 @@
         <v>49</v>
       </c>
       <c r="C170" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
         <v>8</v>
       </c>
-      <c r="D170" t="s">
-        <v>11</v>
-      </c>
       <c r="E170">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -4005,13 +4005,13 @@
         <v>49</v>
       </c>
       <c r="C171" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D171" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -4022,13 +4022,13 @@
         <v>49</v>
       </c>
       <c r="C172" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E172">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>7</v>
       </c>
       <c r="E173">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -4059,10 +4059,10 @@
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E174">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -4073,13 +4073,13 @@
         <v>50</v>
       </c>
       <c r="C175" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
       </c>
       <c r="E175">
-        <v>4</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -4090,13 +4090,13 @@
         <v>50</v>
       </c>
       <c r="C176" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E176">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -4107,13 +4107,13 @@
         <v>50</v>
       </c>
       <c r="C177" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -4124,13 +4124,13 @@
         <v>50</v>
       </c>
       <c r="C178" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E178">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -4141,13 +4141,13 @@
         <v>51</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E179">
-        <v>4</v>
+        <v>303</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -4158,13 +4158,13 @@
         <v>51</v>
       </c>
       <c r="C180" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E180">
-        <v>234</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -4175,13 +4175,13 @@
         <v>51</v>
       </c>
       <c r="C181" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E181">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -4192,13 +4192,13 @@
         <v>51</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D182" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E182">
-        <v>303</v>
+        <v>240</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -4212,10 +4212,10 @@
         <v>6</v>
       </c>
       <c r="D183" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E183">
-        <v>368</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -4226,13 +4226,13 @@
         <v>52</v>
       </c>
       <c r="C184" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E184">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -4243,13 +4243,13 @@
         <v>52</v>
       </c>
       <c r="C185" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E185">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -4260,10 +4260,10 @@
         <v>52</v>
       </c>
       <c r="C186" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E186">
         <v>120</v>
@@ -4277,13 +4277,13 @@
         <v>52</v>
       </c>
       <c r="C187" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
         <v>8</v>
       </c>
-      <c r="D187" t="s">
-        <v>10</v>
-      </c>
       <c r="E187">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,10 +4297,10 @@
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E188">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -4311,13 +4311,13 @@
         <v>53</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E189">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -4331,10 +4331,10 @@
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E190">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -4345,7 +4345,7 @@
         <v>53</v>
       </c>
       <c r="C191" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D191" t="s">
         <v>29</v>
@@ -4362,13 +4362,13 @@
         <v>53</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E192">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -4379,13 +4379,13 @@
         <v>53</v>
       </c>
       <c r="C193" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
         <v>8</v>
       </c>
-      <c r="D193" t="s">
-        <v>9</v>
-      </c>
       <c r="E193">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -4396,13 +4396,13 @@
         <v>53</v>
       </c>
       <c r="C194" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E194">
-        <v>244</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -4413,13 +4413,13 @@
         <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E195">
-        <v>20</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -4430,13 +4430,13 @@
         <v>54</v>
       </c>
       <c r="C196" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D196" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E196">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -4447,13 +4447,13 @@
         <v>54</v>
       </c>
       <c r="C197" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E197">
-        <v>96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -4464,10 +4464,10 @@
         <v>54</v>
       </c>
       <c r="C198" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" t="s">
         <v>8</v>
-      </c>
-      <c r="D198" t="s">
-        <v>14</v>
       </c>
       <c r="E198">
         <v>2</v>
@@ -4487,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="E199">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -4498,10 +4498,10 @@
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D200" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E200">
         <v>4</v>
@@ -4515,13 +4515,13 @@
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E201">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -4532,13 +4532,13 @@
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D202" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E202">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -4549,13 +4549,13 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
         <v>8</v>
       </c>
-      <c r="D203" t="s">
-        <v>15</v>
-      </c>
       <c r="E203">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -4566,13 +4566,13 @@
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E204">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -4583,13 +4583,13 @@
         <v>56</v>
       </c>
       <c r="C205" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D205" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E205">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -4600,13 +4600,13 @@
         <v>56</v>
       </c>
       <c r="C206" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E206">
-        <v>214</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -4620,10 +4620,10 @@
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E207">
-        <v>131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -4634,13 +4634,13 @@
         <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E208">
-        <v>58</v>
+        <v>214</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -4651,13 +4651,13 @@
         <v>57</v>
       </c>
       <c r="C209" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D209" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E209">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -4668,10 +4668,10 @@
         <v>57</v>
       </c>
       <c r="C210" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E210">
         <v>20</v>
@@ -4685,10 +4685,10 @@
         <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E211">
         <v>20</v>
@@ -4702,13 +4702,13 @@
         <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -4722,10 +4722,10 @@
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E213">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -4736,13 +4736,13 @@
         <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E214">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -4753,13 +4753,13 @@
         <v>58</v>
       </c>
       <c r="C215" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
       </c>
       <c r="E215">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -4770,13 +4770,13 @@
         <v>58</v>
       </c>
       <c r="C216" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E216">
-        <v>57</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -4787,13 +4787,13 @@
         <v>58</v>
       </c>
       <c r="C217" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E217">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -4804,13 +4804,13 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E218">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -4821,13 +4821,13 @@
         <v>59</v>
       </c>
       <c r="C219" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D219" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E219">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -4838,10 +4838,10 @@
         <v>59</v>
       </c>
       <c r="C220" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E220">
         <v>48</v>
@@ -4858,10 +4858,10 @@
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E221">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -4872,13 +4872,13 @@
         <v>59</v>
       </c>
       <c r="C222" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
         <v>8</v>
       </c>
-      <c r="D222" t="s">
-        <v>11</v>
-      </c>
       <c r="E222">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -4889,10 +4889,10 @@
         <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E223">
         <v>135</v>
@@ -4906,13 +4906,13 @@
         <v>60</v>
       </c>
       <c r="C224" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E224">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -4923,13 +4923,13 @@
         <v>60</v>
       </c>
       <c r="C225" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D225" t="s">
         <v>11</v>
       </c>
       <c r="E225">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -4940,13 +4940,13 @@
         <v>60</v>
       </c>
       <c r="C226" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
       </c>
       <c r="E226">
-        <v>107</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E227">
         <v>27</v>
@@ -4974,13 +4974,13 @@
         <v>60</v>
       </c>
       <c r="C228" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E228">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -4991,13 +4991,13 @@
         <v>60</v>
       </c>
       <c r="C229" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" t="s">
         <v>8</v>
       </c>
-      <c r="D229" t="s">
-        <v>12</v>
-      </c>
       <c r="E229">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -5014,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="E230">
-        <v>111</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -5025,13 +5025,13 @@
         <v>61</v>
       </c>
       <c r="C231" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D231" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E231">
-        <v>173</v>
+        <v>265</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -5042,13 +5042,13 @@
         <v>61</v>
       </c>
       <c r="C232" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D232" t="s">
         <v>11</v>
       </c>
       <c r="E232">
-        <v>16</v>
+        <v>173</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -5059,13 +5059,13 @@
         <v>61</v>
       </c>
       <c r="C233" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E233">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -5076,13 +5076,13 @@
         <v>61</v>
       </c>
       <c r="C234" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E234">
-        <v>2</v>
+        <v>202</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -5093,13 +5093,13 @@
         <v>61</v>
       </c>
       <c r="C235" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" t="s">
         <v>8</v>
       </c>
-      <c r="D235" t="s">
-        <v>15</v>
-      </c>
       <c r="E235">
-        <v>202</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -5113,10 +5113,10 @@
         <v>6</v>
       </c>
       <c r="D236" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E236">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -5127,13 +5127,13 @@
         <v>62</v>
       </c>
       <c r="C237" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E237">
-        <v>4220</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -5147,10 +5147,10 @@
         <v>6</v>
       </c>
       <c r="D238" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E238">
-        <v>3622</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -5161,13 +5161,13 @@
         <v>62</v>
       </c>
       <c r="C239" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E239">
-        <v>1</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -5178,13 +5178,13 @@
         <v>62</v>
       </c>
       <c r="C240" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D240" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E240">
-        <v>1183</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -5195,13 +5195,13 @@
         <v>62</v>
       </c>
       <c r="C241" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" t="s">
         <v>8</v>
       </c>
-      <c r="D241" t="s">
-        <v>11</v>
-      </c>
       <c r="E241">
-        <v>571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -5212,13 +5212,13 @@
         <v>62</v>
       </c>
       <c r="C242" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E242">
-        <v>5298</v>
+        <v>571</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -5229,10 +5229,10 @@
         <v>62</v>
       </c>
       <c r="C243" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E243">
         <v>975</v>
@@ -5246,13 +5246,13 @@
         <v>63</v>
       </c>
       <c r="C244" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D244" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E244">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -5266,10 +5266,10 @@
         <v>6</v>
       </c>
       <c r="D245" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E245">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -5280,13 +5280,13 @@
         <v>63</v>
       </c>
       <c r="C246" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" t="s">
+        <v>13</v>
+      </c>
+      <c r="E246">
         <v>8</v>
-      </c>
-      <c r="D246" t="s">
-        <v>15</v>
-      </c>
-      <c r="E246">
-        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>63</v>
       </c>
       <c r="C247" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" t="s">
         <v>8</v>
-      </c>
-      <c r="D247" t="s">
-        <v>14</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -5314,13 +5314,13 @@
         <v>63</v>
       </c>
       <c r="C248" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E248">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -5331,13 +5331,13 @@
         <v>64</v>
       </c>
       <c r="C249" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D249" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E249">
-        <v>2</v>
+        <v>300</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -5351,10 +5351,10 @@
         <v>6</v>
       </c>
       <c r="D250" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E250">
-        <v>6179</v>
+        <v>875</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -5365,13 +5365,13 @@
         <v>64</v>
       </c>
       <c r="C251" t="s">
+        <v>6</v>
+      </c>
+      <c r="D251" t="s">
         <v>8</v>
       </c>
-      <c r="D251" t="s">
-        <v>11</v>
-      </c>
       <c r="E251">
-        <v>875</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -5382,13 +5382,13 @@
         <v>64</v>
       </c>
       <c r="C252" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D252" t="s">
         <v>15</v>
       </c>
       <c r="E252">
-        <v>300</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -5399,10 +5399,10 @@
         <v>65</v>
       </c>
       <c r="C253" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D253" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E253">
         <v>386</v>
@@ -5416,13 +5416,13 @@
         <v>65</v>
       </c>
       <c r="C254" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E254">
-        <v>987</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -5433,10 +5433,10 @@
         <v>65</v>
       </c>
       <c r="C255" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E255">
         <v>834</v>
@@ -5450,13 +5450,13 @@
         <v>65</v>
       </c>
       <c r="C256" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
         <v>8</v>
       </c>
-      <c r="D256" t="s">
-        <v>10</v>
-      </c>
       <c r="E256">
-        <v>255</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -5467,13 +5467,13 @@
         <v>65</v>
       </c>
       <c r="C257" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D257" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E257">
-        <v>2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -5484,13 +5484,13 @@
         <v>65</v>
       </c>
       <c r="C258" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E258">
-        <v>113</v>
+        <v>987</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -5501,13 +5501,13 @@
         <v>66</v>
       </c>
       <c r="C259" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E259">
-        <v>1</v>
+        <v>411</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -5518,13 +5518,13 @@
         <v>66</v>
       </c>
       <c r="C260" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D260" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E260">
-        <v>411</v>
+        <v>78</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -5535,13 +5535,13 @@
         <v>66</v>
       </c>
       <c r="C261" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D261" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E261">
-        <v>535</v>
+        <v>374</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -5552,13 +5552,13 @@
         <v>66</v>
       </c>
       <c r="C262" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D262" t="s">
         <v>11</v>
       </c>
       <c r="E262">
-        <v>256</v>
+        <v>535</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -5569,13 +5569,13 @@
         <v>66</v>
       </c>
       <c r="C263" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" t="s">
         <v>8</v>
       </c>
-      <c r="D263" t="s">
-        <v>12</v>
-      </c>
       <c r="E263">
-        <v>374</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -5586,13 +5586,13 @@
         <v>66</v>
       </c>
       <c r="C264" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D264" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E264">
-        <v>78</v>
+        <v>256</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -5603,10 +5603,10 @@
         <v>66</v>
       </c>
       <c r="C265" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D265" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E265">
         <v>192</v>
@@ -5620,10 +5620,10 @@
         <v>67</v>
       </c>
       <c r="C266" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D266" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E266">
         <v>150</v>
@@ -5637,10 +5637,10 @@
         <v>67</v>
       </c>
       <c r="C267" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E267">
         <v>97</v>
@@ -5654,10 +5654,10 @@
         <v>67</v>
       </c>
       <c r="C268" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D268" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E268">
         <v>35</v>
@@ -5671,10 +5671,10 @@
         <v>67</v>
       </c>
       <c r="C269" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" t="s">
         <v>8</v>
-      </c>
-      <c r="D269" t="s">
-        <v>14</v>
       </c>
       <c r="E269">
         <v>3</v>
@@ -5688,10 +5688,10 @@
         <v>67</v>
       </c>
       <c r="C270" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D270" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E270">
         <v>10</v>
@@ -5705,13 +5705,13 @@
         <v>68</v>
       </c>
       <c r="C271" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D271" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E271">
-        <v>7</v>
+        <v>310</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -5722,13 +5722,13 @@
         <v>68</v>
       </c>
       <c r="C272" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D272" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E272">
-        <v>73</v>
+        <v>144</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -5739,13 +5739,13 @@
         <v>68</v>
       </c>
       <c r="C273" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D273" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E273">
-        <v>144</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -5756,13 +5756,13 @@
         <v>68</v>
       </c>
       <c r="C274" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E274">
-        <v>1680</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -5773,13 +5773,13 @@
         <v>68</v>
       </c>
       <c r="C275" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" t="s">
         <v>8</v>
       </c>
-      <c r="D275" t="s">
-        <v>15</v>
-      </c>
       <c r="E275">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -5793,10 +5793,10 @@
         <v>6</v>
       </c>
       <c r="D276" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E276">
-        <v>310</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -5807,13 +5807,13 @@
         <v>69</v>
       </c>
       <c r="C277" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E277">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -5824,13 +5824,13 @@
         <v>69</v>
       </c>
       <c r="C278" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D278" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E278">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -5841,13 +5841,13 @@
         <v>69</v>
       </c>
       <c r="C279" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" t="s">
         <v>8</v>
       </c>
-      <c r="D279" t="s">
-        <v>15</v>
-      </c>
       <c r="E279">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -5858,13 +5858,13 @@
         <v>69</v>
       </c>
       <c r="C280" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D280" t="s">
+        <v>7</v>
+      </c>
+      <c r="E280">
         <v>10</v>
-      </c>
-      <c r="E280">
-        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -5875,13 +5875,13 @@
         <v>70</v>
       </c>
       <c r="C281" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D281" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E281">
-        <v>38</v>
+        <v>527</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -5892,13 +5892,13 @@
         <v>70</v>
       </c>
       <c r="C282" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D282" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E282">
-        <v>16</v>
+        <v>873</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -5912,10 +5912,10 @@
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E283">
-        <v>527</v>
+        <v>38</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -5926,13 +5926,13 @@
         <v>70</v>
       </c>
       <c r="C284" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D284" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E284">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -5943,13 +5943,13 @@
         <v>70</v>
       </c>
       <c r="C285" t="s">
+        <v>6</v>
+      </c>
+      <c r="D285" t="s">
         <v>8</v>
       </c>
-      <c r="D285" t="s">
-        <v>9</v>
-      </c>
       <c r="E285">
-        <v>873</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -5960,13 +5960,13 @@
         <v>70</v>
       </c>
       <c r="C286" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D286" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E286">
-        <v>295</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -5977,13 +5977,13 @@
         <v>71</v>
       </c>
       <c r="C287" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D287" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E287">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -5994,13 +5994,13 @@
         <v>71</v>
       </c>
       <c r="C288" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E288">
-        <v>97</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -6011,13 +6011,13 @@
         <v>71</v>
       </c>
       <c r="C289" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" t="s">
         <v>8</v>
       </c>
-      <c r="D289" t="s">
-        <v>11</v>
-      </c>
       <c r="E289">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -6034,7 +6034,7 @@
         <v>7</v>
       </c>
       <c r="E290">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -6045,13 +6045,13 @@
         <v>72</v>
       </c>
       <c r="C291" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D291" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E291">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -6062,13 +6062,13 @@
         <v>72</v>
       </c>
       <c r="C292" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D292" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E292">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -6079,13 +6079,13 @@
         <v>72</v>
       </c>
       <c r="C293" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" t="s">
         <v>8</v>
       </c>
-      <c r="D293" t="s">
-        <v>11</v>
-      </c>
       <c r="E293">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -6096,10 +6096,10 @@
         <v>72</v>
       </c>
       <c r="C294" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D294" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -6113,13 +6113,13 @@
         <v>73</v>
       </c>
       <c r="C295" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E295">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -6130,13 +6130,13 @@
         <v>73</v>
       </c>
       <c r="C296" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D296" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E296">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -6147,13 +6147,13 @@
         <v>73</v>
       </c>
       <c r="C297" t="s">
+        <v>6</v>
+      </c>
+      <c r="D297" t="s">
         <v>8</v>
       </c>
-      <c r="D297" t="s">
-        <v>10</v>
-      </c>
       <c r="E297">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -6164,13 +6164,13 @@
         <v>74</v>
       </c>
       <c r="C298" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298">
         <v>8</v>
-      </c>
-      <c r="D298" t="s">
-        <v>12</v>
-      </c>
-      <c r="E298">
-        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -6181,10 +6181,10 @@
         <v>74</v>
       </c>
       <c r="C299" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D299" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E299">
         <v>1</v>
@@ -6198,13 +6198,13 @@
         <v>74</v>
       </c>
       <c r="C300" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D300" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E300">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -6215,10 +6215,10 @@
         <v>74</v>
       </c>
       <c r="C301" t="s">
+        <v>6</v>
+      </c>
+      <c r="D301" t="s">
         <v>8</v>
-      </c>
-      <c r="D301" t="s">
-        <v>14</v>
       </c>
       <c r="E301">
         <v>1</v>
@@ -6232,13 +6232,13 @@
         <v>74</v>
       </c>
       <c r="C302" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D302" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E302">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -6249,10 +6249,10 @@
         <v>75</v>
       </c>
       <c r="C303" t="s">
+        <v>6</v>
+      </c>
+      <c r="D303" t="s">
         <v>8</v>
-      </c>
-      <c r="D303" t="s">
-        <v>14</v>
       </c>
       <c r="E303">
         <v>1</v>
@@ -6266,10 +6266,10 @@
         <v>75</v>
       </c>
       <c r="C304" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D304" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E304">
         <v>717</v>
@@ -6283,13 +6283,13 @@
         <v>75</v>
       </c>
       <c r="C305" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D305" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -6300,13 +6300,13 @@
         <v>75</v>
       </c>
       <c r="C306" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D306" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E306">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -6317,10 +6317,10 @@
         <v>75</v>
       </c>
       <c r="C307" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E307">
         <v>325</v>
@@ -6334,13 +6334,13 @@
         <v>75</v>
       </c>
       <c r="C308" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D308" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E308">
-        <v>65</v>
+        <v>560</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -6351,13 +6351,13 @@
         <v>75</v>
       </c>
       <c r="C309" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D309" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E309">
-        <v>560</v>
+        <v>39</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -6368,13 +6368,13 @@
         <v>76</v>
       </c>
       <c r="C310" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D310" t="s">
         <v>10</v>
       </c>
       <c r="E310">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -6385,13 +6385,13 @@
         <v>76</v>
       </c>
       <c r="C311" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D311" t="s">
         <v>9</v>
       </c>
       <c r="E311">
-        <v>112</v>
+        <v>288</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -6402,13 +6402,13 @@
         <v>76</v>
       </c>
       <c r="C312" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D312" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E312">
-        <v>290</v>
+        <v>112</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -6419,10 +6419,10 @@
         <v>76</v>
       </c>
       <c r="C313" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E313">
         <v>218</v>
@@ -6436,10 +6436,10 @@
         <v>77</v>
       </c>
       <c r="C314" t="s">
+        <v>6</v>
+      </c>
+      <c r="D314" t="s">
         <v>8</v>
-      </c>
-      <c r="D314" t="s">
-        <v>14</v>
       </c>
       <c r="E314">
         <v>8</v>
@@ -6453,13 +6453,13 @@
         <v>77</v>
       </c>
       <c r="C315" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E315">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -6470,10 +6470,10 @@
         <v>77</v>
       </c>
       <c r="C316" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D316" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E316">
         <v>58</v>
@@ -6487,13 +6487,13 @@
         <v>77</v>
       </c>
       <c r="C317" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D317" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E317">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -6504,10 +6504,10 @@
         <v>77</v>
       </c>
       <c r="C318" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D318" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E318">
         <v>16</v>
@@ -6521,10 +6521,10 @@
         <v>78</v>
       </c>
       <c r="C319" t="s">
+        <v>6</v>
+      </c>
+      <c r="D319" t="s">
         <v>8</v>
-      </c>
-      <c r="D319" t="s">
-        <v>14</v>
       </c>
       <c r="E319">
         <v>7</v>
@@ -6538,10 +6538,10 @@
         <v>78</v>
       </c>
       <c r="C320" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D320" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E320">
         <v>404</v>
@@ -6555,10 +6555,10 @@
         <v>78</v>
       </c>
       <c r="C321" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E321">
         <v>785</v>
@@ -6572,10 +6572,10 @@
         <v>78</v>
       </c>
       <c r="C322" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D322" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E322">
         <v>8280</v>
@@ -6589,10 +6589,10 @@
         <v>78</v>
       </c>
       <c r="C323" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D323" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E323">
         <v>562</v>
@@ -6606,10 +6606,10 @@
         <v>78</v>
       </c>
       <c r="C324" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D324" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E324">
         <v>746</v>
@@ -6623,10 +6623,10 @@
         <v>78</v>
       </c>
       <c r="C325" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E325">
         <v>1974</v>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -444,11 +444,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,43 +458,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2691</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,20 +504,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -527,20 +527,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>432</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,20 +573,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,43 +596,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1240</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -642,20 +642,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>580</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -665,43 +665,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,43 +711,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>804</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -757,20 +757,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>254</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -780,20 +780,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1311</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -803,20 +803,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -826,20 +826,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3724</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -872,20 +872,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6287</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -895,39 +895,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1056</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9260</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -964,20 +964,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -987,20 +987,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,43 +1056,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1125,66 +1125,66 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>65</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,43 +1194,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1240,20 +1240,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1272,11 +1272,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1286,43 +1286,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>340</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1336,62 +1336,62 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1256</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1075</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>800</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1401,20 +1401,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1327</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1424,20 +1424,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>417</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1470,43 +1470,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>629</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,20 +1516,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>21</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1539,43 +1539,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>615</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1608,20 +1608,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1631,43 +1631,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1677,43 +1677,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>756</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4524</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1723,20 +1723,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1746,20 +1746,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1769,20 +1769,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>439</v>
+        <v>524</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1815,43 +1815,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>43</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>551</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1861,20 +1861,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1884,20 +1884,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>120</v>
+        <v>34063</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1907,16 +1907,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2248</v>
+        <v>37636</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1492</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1976,16 +1976,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3477</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1999,16 +1999,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35009</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2017,48 +2017,48 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219</v>
+        <v>886</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37052</v>
+        <v>162087</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2068,43 +2068,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>39786</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>257</v>
+        <v>176905</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2114,39 +2114,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>483</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2160,16 +2160,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>151539</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2183,43 +2183,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>39888</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>175328</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2229,43 +2229,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>12146</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4256</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>22668</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2302,12 +2302,12 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2321,16 +2321,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>78</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2367,20 +2367,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2390,20 +2390,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>162</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2440,12 +2440,12 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>290</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2505,39 +2505,39 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>516</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2578,12 +2578,12 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2597,16 +2597,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>607</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2643,16 +2643,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>705</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2666,16 +2666,16 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>80</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2689,16 +2689,16 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>863</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2712,16 +2712,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2884</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2758,16 +2758,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4895</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2776,21 +2776,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>10</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>391</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2827,16 +2827,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2850,16 +2850,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>66</v>
+        <v>974</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>704</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2900,12 +2900,12 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2914,21 +2914,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>928</v>
+        <v>755</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>695</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2965,16 +2965,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>8</v>
+        <v>817</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2988,16 +2988,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1241</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3011,16 +3011,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3034,16 +3034,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>19919</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>283</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3075,21 +3075,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3098,21 +3098,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1240</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>186</v>
+        <v>337</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>264</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3176,12 +3176,12 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>178</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3195,20 +3195,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3218,39 +3218,39 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>28</v>
+        <v>172</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3287,16 +3287,16 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>234</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3310,16 +3310,16 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>47</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3333,20 +3333,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3356,20 +3356,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>380</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3383,12 +3383,12 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1733</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3406,12 +3406,12 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>528</v>
+        <v>726</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3420,67 +3420,67 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>8</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>7385</v>
+        <v>701</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9678</v>
+        <v>315</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3494,16 +3494,16 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3517,20 +3517,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>868</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3540,20 +3540,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>282</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3563,16 +3563,16 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3581,21 +3581,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3604,21 +3604,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -3632,43 +3632,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>142</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3678,20 +3678,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,16 +3701,16 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,20 +3793,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,16 +3816,16 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -3839,16 +3839,16 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3862,20 +3862,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3908,20 +3908,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3954,20 +3954,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>843</v>
+        <v>85</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3977,20 +3977,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1019</v>
+        <v>54</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,20 +4000,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,16 +4023,16 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4064,48 +4064,48 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3231</v>
+        <v>687</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>48</v>
+        <v>964</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4115,43 +4115,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>531</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4161,66 +4161,66 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>280</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4230,20 +4230,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4253,16 +4253,16 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4276,16 +4276,16 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4299,43 +4299,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>109</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4345,20 +4345,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4368,43 +4368,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>69</v>
+        <v>283</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4418,16 +4418,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4437,20 +4437,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4460,20 +4460,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4483,16 +4483,16 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -4515,34 +4515,34 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>368</v>
+        <v>96</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4552,43 +4552,43 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>303</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4598,89 +4598,89 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>234</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>58</v>
+        <v>295</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>38</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4694,16 +4694,16 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>48</v>
+        <v>206</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4713,20 +4713,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4</v>
+        <v>214</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,43 +4736,43 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4782,20 +4782,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4805,20 +4805,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>298</v>
+        <v>48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4828,39 +4828,39 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -4878,12 +4878,12 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -4897,43 +4897,43 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4943,20 +4943,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4966,16 +4966,16 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4984,48 +4984,48 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5035,20 +5035,20 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5062,12 +5062,12 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5108,62 +5108,62 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>131</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5173,16 +5173,16 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5196,43 +5196,43 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>214</v>
+        <v>44</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5242,43 +5242,43 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20</v>
+        <v>147</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5292,16 +5292,16 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5320,7 +5320,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5357,20 +5357,20 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5380,20 +5380,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5412,67 +5412,67 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5481,11 +5481,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5495,20 +5495,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5518,20 +5518,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,66 +5541,66 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>135</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>111</v>
+        <v>25</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5610,20 +5610,20 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5637,16 +5637,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5656,20 +5656,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,16 +5679,16 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -5697,48 +5697,48 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>16</v>
+        <v>113</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>265</v>
+        <v>105</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,16 +5752,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>257</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5771,20 +5771,20 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>202</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,20 +5794,20 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5817,20 +5817,20 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5840,20 +5840,20 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>173</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5867,16 +5867,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3622</v>
+        <v>268</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5913,16 +5913,16 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1183</v>
+        <v>199</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5936,16 +5936,16 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5298</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5964,11 +5964,11 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>571</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>975</v>
+        <v>85</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>21</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6070,20 +6070,20 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>8</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6116,20 +6116,20 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>23</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6139,20 +6139,20 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6166,16 +6166,16 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>875</v>
+        <v>587</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6185,20 +6185,20 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2</v>
+        <v>944</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6212,39 +6212,39 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6179</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>386</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6254,20 +6254,20 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>834</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,20 +6277,20 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>113</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6300,20 +6300,20 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>987</v>
+        <v>283</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6323,20 +6323,20 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>477</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>255</v>
+        <v>547</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,20 +6369,20 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>411</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6392,66 +6392,66 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>374</v>
+        <v>70</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>535</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>854</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6488,62 +6488,62 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>256</v>
+        <v>106</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>192</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,43 +6553,43 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>97</v>
+        <v>277</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>35</v>
+        <v>202</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,20 +6599,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>468</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6626,62 +6626,62 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>310</v>
+        <v>434</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>144</v>
+        <v>307</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6691,20 +6691,20 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6714,20 +6714,20 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>11</v>
+        <v>256</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6737,43 +6737,43 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>7</v>
+        <v>343</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1680</v>
+        <v>149</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,20 +6783,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6838,11 +6838,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6856,39 +6856,39 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>527</v>
+        <v>352</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,20 +6898,20 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>873</v>
+        <v>143</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6925,16 +6925,16 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6948,16 +6948,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>295</v>
+        <v>60</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6971,16 +6971,16 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,43 +6990,43 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>16</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,20 +7036,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7059,20 +7059,20 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7082,20 +7082,20 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7109,62 +7109,62 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>1</v>
+        <v>538</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2</v>
+        <v>858</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7197,20 +7197,20 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7220,20 +7220,20 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>48</v>
+        <v>297</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7247,16 +7247,16 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7270,39 +7270,39 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7316,16 +7316,16 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7339,16 +7339,16 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,20 +7358,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,20 +7381,20 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,20 +7404,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>717</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7427,20 +7427,20 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,20 +7450,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7473,20 +7473,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>325</v>
+        <v>66</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,20 +7496,20 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>560</v>
+        <v>48</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,43 +7519,43 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>290</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,20 +7565,20 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>288</v>
+        <v>13</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7588,20 +7588,20 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,20 +7611,20 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>218</v>
+        <v>837</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,20 +7634,20 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7657,20 +7657,20 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7680,20 +7680,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>58</v>
+        <v>311</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7707,16 +7707,16 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>54</v>
+        <v>544</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,20 +7749,20 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,20 +7772,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>404</v>
+        <v>290</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,43 +7795,43 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>785</v>
+        <v>188</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>8280</v>
+        <v>318</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,57 +7841,310 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>562</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>746</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
+          <t>3151 - EMC</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>3151 - EMC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADA</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>3151 - EMC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>3151 - EMC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
           <t>4291 - FES</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Inativo</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>OUTRAS</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Terceirizado</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>TERCEIRIZADO</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
         <is>
           <t>ESPECIALIZADA</t>
         </is>
       </c>
-      <c r="E325" t="n">
-        <v>1974</v>
+      <c r="E336" t="n">
+        <v>1849</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -471,21 +471,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>830</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>395</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -517,21 +517,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>565</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="6">
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="7">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>236</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -586,7 +586,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1259</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -632,7 +632,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1037</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +655,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -665,11 +665,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -678,21 +678,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6352</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13">
@@ -701,21 +701,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9150</v>
+        <v>830</v>
       </c>
     </row>
     <row r="14">
@@ -724,7 +724,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -747,7 +747,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -757,11 +757,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3652</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -770,7 +770,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1021 - TCEMG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -780,11 +780,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -803,11 +803,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -849,11 +849,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -862,7 +862,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -872,11 +872,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="21">
@@ -885,7 +885,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -895,11 +895,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="22">
@@ -908,21 +908,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="23">
@@ -931,7 +931,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -941,11 +941,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -964,11 +964,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -977,21 +977,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1023,21 +1023,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1092,21 +1092,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>468</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>312</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1138,21 +1138,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1161,21 +1161,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1260</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1092</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>761</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1240,11 +1240,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1335</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>432</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -1276,21 +1276,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1332,11 +1332,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>39</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41">
@@ -1345,21 +1345,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>432</v>
       </c>
     </row>
     <row r="43">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
@@ -1414,21 +1414,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>761</v>
       </c>
     </row>
     <row r="45">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>629</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="47">
@@ -1483,21 +1483,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4428</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="48">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1213</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>750</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -1552,21 +1552,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -1644,21 +1644,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>430</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1677,11 +1677,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>41</v>
+        <v>750</v>
       </c>
     </row>
     <row r="56">
@@ -1690,21 +1690,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>93</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="57">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="59">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>119</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>524</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2334</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1838,11 +1838,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1598</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1861,11 +1861,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3507</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1884,11 +1884,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>34063</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65">
@@ -1897,21 +1897,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>216</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66">
@@ -1920,21 +1920,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>37636</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -1943,21 +1943,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>260</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2017,16 +2017,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>886</v>
+        <v>260</v>
       </c>
     </row>
     <row r="71">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>162087</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>39786</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2091,11 +2091,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>176905</v>
+        <v>37636</v>
       </c>
     </row>
     <row r="74">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>15695</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="75">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4338</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="76">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2160,11 +2160,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22985</v>
+        <v>34063</v>
       </c>
     </row>
     <row r="77">
@@ -2173,21 +2173,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>886</v>
       </c>
     </row>
     <row r="78">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>84</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="79">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -2242,21 +2242,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>115</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="81">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="82">
@@ -2288,21 +2288,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>176905</v>
       </c>
     </row>
     <row r="83">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>159</v>
+        <v>162087</v>
       </c>
     </row>
     <row r="84">
@@ -2334,21 +2334,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>285</v>
+        <v>39786</v>
       </c>
     </row>
     <row r="85">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>200</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="86">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2449,21 +2449,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90">
@@ -2472,21 +2472,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2495,21 +2495,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>516</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92">
@@ -2518,21 +2518,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2551,11 +2551,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>123</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95">
@@ -2587,21 +2587,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96">
@@ -2610,21 +2610,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97">
@@ -2633,21 +2633,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>705</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3052</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>516</v>
       </c>
     </row>
     <row r="103">
@@ -2771,21 +2771,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>397</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2827,11 +2827,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>974</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>81</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="108">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2896,11 +2896,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>7</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="109">
@@ -2909,21 +2909,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>755</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>14404</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,11 +2965,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>817</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112">
@@ -2978,21 +2978,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>397</v>
       </c>
     </row>
     <row r="113">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1014</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3034,11 +3034,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1356</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
@@ -3047,21 +3047,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2690</v>
+        <v>974</v>
       </c>
     </row>
     <row r="116">
@@ -3070,21 +3070,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="118">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>337</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -3139,21 +3139,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1208</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="120">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>135</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="121">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>817</v>
       </c>
     </row>
     <row r="122">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>172</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="123">
@@ -3231,21 +3231,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>189</v>
+        <v>755</v>
       </c>
     </row>
     <row r="124">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>30</v>
+        <v>172</v>
       </c>
     </row>
     <row r="125">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3287,11 +3287,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="126">
@@ -3300,21 +3300,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>250</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>52</v>
+        <v>337</v>
       </c>
     </row>
     <row r="128">
@@ -3346,21 +3346,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="129">
@@ -3369,21 +3369,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1117</v>
+        <v>189</v>
       </c>
     </row>
     <row r="130">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>726</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3415,21 +3415,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1584</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>701</v>
+        <v>250</v>
       </c>
     </row>
     <row r="133">
@@ -3461,21 +3461,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>10389</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3517,11 +3517,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1332</v>
+        <v>52</v>
       </c>
     </row>
     <row r="136">
@@ -3530,21 +3530,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>14</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="137">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3563,11 +3563,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
@@ -3576,21 +3576,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>18</v>
+        <v>726</v>
       </c>
     </row>
     <row r="139">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3609,11 +3609,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>21</v>
+        <v>701</v>
       </c>
     </row>
     <row r="140">
@@ -3622,21 +3622,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>140</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="141">
@@ -3645,21 +3645,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>315</v>
       </c>
     </row>
     <row r="142">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>13</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="143">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="144">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3724,11 +3724,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146">
@@ -3760,21 +3760,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150">
@@ -3852,21 +3852,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="153">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="156">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>687</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>964</v>
+        <v>85</v>
       </c>
     </row>
     <row r="161">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>531</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4128,21 +4128,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3362</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="164">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4197,21 +4197,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4230,11 +4230,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="167">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>38</v>
+        <v>531</v>
       </c>
     </row>
     <row r="169">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>58</v>
+        <v>964</v>
       </c>
     </row>
     <row r="170">
@@ -4312,21 +4312,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="171">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>150</v>
+        <v>687</v>
       </c>
     </row>
     <row r="172">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173">
@@ -4381,21 +4381,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>283</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="175">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4460,11 +4460,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4519,21 +4519,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>96</v>
+        <v>283</v>
       </c>
     </row>
     <row r="180">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181">
@@ -4565,21 +4565,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="183">
@@ -4611,21 +4611,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>295</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185">
@@ -4657,21 +4657,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>387</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4680,21 +4680,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>206</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>214</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -4749,21 +4749,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
     </row>
     <row r="190">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4805,11 +4805,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193">
@@ -4841,21 +4841,21 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>63</v>
+        <v>295</v>
       </c>
     </row>
     <row r="194">
@@ -4864,21 +4864,21 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>387</v>
       </c>
     </row>
     <row r="195">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>206</v>
       </c>
     </row>
     <row r="197">
@@ -4933,21 +4933,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="198">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>101</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199">
@@ -4979,21 +4979,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="200">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="202">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="204">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5104,11 +5104,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -5140,21 +5140,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="207">
@@ -5163,21 +5163,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="208">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5219,11 +5219,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
     </row>
     <row r="211">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="214">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216">
@@ -5370,21 +5370,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="217">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
     </row>
     <row r="218">
@@ -5416,21 +5416,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5449,11 +5449,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220">
@@ -5462,21 +5462,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="222">
@@ -5508,21 +5508,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="223">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225">
@@ -5577,21 +5577,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5610,11 +5610,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,11 +5633,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="228">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="229">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,11 +5679,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="230">
@@ -5692,21 +5692,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>113</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5725,11 +5725,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
     </row>
     <row r="233">
@@ -5761,21 +5761,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="234">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5817,11 +5817,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="236">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5840,11 +5840,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -5853,21 +5853,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>268</v>
+        <v>102</v>
       </c>
     </row>
     <row r="238">
@@ -5876,21 +5876,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>250</v>
+        <v>113</v>
       </c>
     </row>
     <row r="239">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,11 +5909,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>199</v>
+        <v>26</v>
       </c>
     </row>
     <row r="240">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5932,11 +5932,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>165</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="242">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -5991,21 +5991,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="244">
@@ -6014,21 +6014,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3222</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3963</v>
+        <v>268</v>
       </c>
     </row>
     <row r="246">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3879</v>
+        <v>250</v>
       </c>
     </row>
     <row r="247">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4103</v>
+        <v>199</v>
       </c>
     </row>
     <row r="248">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1482</v>
+        <v>165</v>
       </c>
     </row>
     <row r="249">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>587</v>
+        <v>20</v>
       </c>
     </row>
     <row r="251">
@@ -6175,21 +6175,21 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>944</v>
+        <v>85</v>
       </c>
     </row>
     <row r="252">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>21</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="253">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>10</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="254">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6254,11 +6254,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>944</v>
       </c>
     </row>
     <row r="255">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>20</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="256">
@@ -6290,21 +6290,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>283</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="257">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>477</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>547</v>
+        <v>587</v>
       </c>
     </row>
     <row r="259">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>29</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="260">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262">
@@ -6428,21 +6428,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>423</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>854</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>106</v>
+        <v>283</v>
       </c>
     </row>
     <row r="265">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1072</v>
+        <v>477</v>
       </c>
     </row>
     <row r="266">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6530,11 +6530,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2</v>
+        <v>547</v>
       </c>
     </row>
     <row r="267">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>277</v>
+        <v>29</v>
       </c>
     </row>
     <row r="268">
@@ -6566,21 +6566,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>202</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269">
@@ -6589,21 +6589,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>468</v>
+        <v>70</v>
       </c>
     </row>
     <row r="270">
@@ -6612,21 +6612,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="271">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>434</v>
+        <v>854</v>
       </c>
     </row>
     <row r="272">
@@ -6658,21 +6658,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>307</v>
+        <v>106</v>
       </c>
     </row>
     <row r="273">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6691,11 +6691,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="274">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6714,11 +6714,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>343</v>
+        <v>277</v>
       </c>
     </row>
     <row r="276">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="277">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>115</v>
+        <v>468</v>
       </c>
     </row>
     <row r="278">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
     </row>
     <row r="279">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6829,11 +6829,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4</v>
+        <v>434</v>
       </c>
     </row>
     <row r="280">
@@ -6842,21 +6842,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="281">
@@ -6865,21 +6865,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>352</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>143</v>
+        <v>256</v>
       </c>
     </row>
     <row r="283">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6921,11 +6921,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>25</v>
+        <v>343</v>
       </c>
     </row>
     <row r="284">
@@ -6934,21 +6934,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>60</v>
+        <v>149</v>
       </c>
     </row>
     <row r="285">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="286">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1674</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287">
@@ -7003,21 +7003,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289">
@@ -7049,21 +7049,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>352</v>
       </c>
     </row>
     <row r="290">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7082,11 +7082,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4</v>
+        <v>143</v>
       </c>
     </row>
     <row r="291">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="292">
@@ -7118,21 +7118,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="293">
@@ -7141,21 +7141,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>538</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>858</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="295">
@@ -7187,21 +7187,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="296">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7220,11 +7220,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>297</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7266,11 +7266,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="299">
@@ -7279,21 +7279,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300">
@@ -7302,21 +7302,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="301">
@@ -7325,21 +7325,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>9</v>
+        <v>538</v>
       </c>
     </row>
     <row r="302">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,11 +7358,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>87</v>
+        <v>858</v>
       </c>
     </row>
     <row r="303">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="304">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6</v>
+        <v>297</v>
       </c>
     </row>
     <row r="305">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307">
@@ -7463,21 +7463,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="308">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="310">
@@ -7532,21 +7532,21 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="311">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,11 +7565,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="312">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="313">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>837</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7657,11 +7657,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="316">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>311</v>
+        <v>48</v>
       </c>
     </row>
     <row r="317">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7703,11 +7703,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>544</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,11 +7749,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="320">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>290</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>188</v>
+        <v>837</v>
       </c>
     </row>
     <row r="322">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7818,11 +7818,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>318</v>
+        <v>56</v>
       </c>
     </row>
     <row r="323">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
@@ -7854,21 +7854,21 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>8</v>
+        <v>311</v>
       </c>
     </row>
     <row r="325">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>43</v>
+        <v>544</v>
       </c>
     </row>
     <row r="326">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="328">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7956,11 +7956,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
     </row>
     <row r="329">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>7</v>
+        <v>188</v>
       </c>
     </row>
     <row r="330">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8002,11 +8002,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>404</v>
+        <v>318</v>
       </c>
     </row>
     <row r="331">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8025,11 +8025,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>715</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332">
@@ -8038,21 +8038,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>7924</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>534</v>
+        <v>43</v>
       </c>
     </row>
     <row r="334">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8094,11 +8094,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>749</v>
+        <v>47</v>
       </c>
     </row>
     <row r="335">
@@ -8107,21 +8107,21 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2006</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336">
@@ -8130,20 +8130,204 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
+          <t>3151 - EMC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
           <t>4291 - FES</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Inativo</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>OUTRAS</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Terceirizado</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>TERCEIRIZADO</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
         <is>
           <t>ESPECIALIZADA</t>
         </is>
       </c>
-      <c r="E336" t="n">
+      <c r="E344" t="n">
         <v>1849</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>172</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125">
@@ -3287,11 +3287,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126">
@@ -3305,16 +3305,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="127">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1208</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3374,16 +3374,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>189</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="130">
@@ -3397,16 +3397,16 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131">
@@ -3425,11 +3425,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3443,16 +3443,16 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>250</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="133">
@@ -3471,11 +3471,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5</v>
+        <v>250</v>
       </c>
     </row>
     <row r="134">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -3535,16 +3535,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1117</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137">
@@ -3563,11 +3563,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>726</v>
+        <v>701</v>
       </c>
     </row>
     <row r="139">
@@ -3604,16 +3604,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>701</v>
+        <v>315</v>
       </c>
     </row>
     <row r="140">
@@ -3627,16 +3627,16 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1584</v>
+        <v>726</v>
       </c>
     </row>
     <row r="141">
@@ -3650,16 +3650,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>315</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="142">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1332</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="143">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>10389</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="144">
@@ -3714,21 +3714,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>18</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="145">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150">
@@ -3857,16 +3857,16 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="151">
@@ -3880,16 +3880,16 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="167">
@@ -4248,16 +4248,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="168">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>964</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3362</v>
+        <v>964</v>
       </c>
     </row>
     <row r="171">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>687</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13</v>
+        <v>687</v>
       </c>
     </row>
     <row r="173">
@@ -4386,16 +4386,16 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="174">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
@@ -4478,16 +4478,16 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>150</v>
+        <v>283</v>
       </c>
     </row>
     <row r="178">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="179">
@@ -4524,16 +4524,16 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>283</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180">
@@ -4552,11 +4552,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="182">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4680,21 +4680,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="187">
@@ -4708,16 +4708,16 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
     </row>
     <row r="189">
@@ -4754,16 +4754,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -4805,11 +4805,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192">
@@ -4818,21 +4818,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>214</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>295</v>
+        <v>387</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>387</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4</v>
+        <v>206</v>
       </c>
     </row>
     <row r="196">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>206</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
@@ -4933,21 +4933,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>63</v>
+        <v>295</v>
       </c>
     </row>
     <row r="198">
@@ -4961,16 +4961,16 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="199">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="201">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
     </row>
     <row r="203">
@@ -5076,16 +5076,16 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
     </row>
     <row r="204">
@@ -5104,11 +5104,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206">
@@ -5163,21 +5163,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="209">
@@ -5214,16 +5214,16 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="210">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -5255,21 +5255,21 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="213">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="215">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="216">
@@ -5370,21 +5370,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
@@ -5421,16 +5421,16 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>44</v>
+        <v>147</v>
       </c>
     </row>
     <row r="219">
@@ -5449,11 +5449,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>23</v>
+        <v>104</v>
       </c>
     </row>
     <row r="220">
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="221">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222">
@@ -5508,21 +5508,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="224">
@@ -5559,16 +5559,16 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="225">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226">
@@ -5610,11 +5610,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227">
@@ -5633,11 +5633,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,11 +5679,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="230">
@@ -5697,16 +5697,16 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="231">
@@ -5725,11 +5725,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="233">
@@ -5761,21 +5761,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
@@ -5812,16 +5812,16 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="236">
@@ -5840,11 +5840,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>102</v>
+        <v>30</v>
       </c>
     </row>
     <row r="238">
@@ -5876,21 +5876,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>113</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
     </row>
     <row r="240">
@@ -5927,16 +5927,16 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>15</v>
+        <v>113</v>
       </c>
     </row>
     <row r="241">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="243">
@@ -6037,21 +6037,21 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6070,11 +6070,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>250</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -6088,16 +6088,16 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>199</v>
+        <v>85</v>
       </c>
     </row>
     <row r="248">
@@ -6111,16 +6111,16 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
     </row>
     <row r="249">
@@ -6139,11 +6139,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
     </row>
     <row r="250">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
     </row>
     <row r="251">
@@ -6180,16 +6180,16 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6198,21 +6198,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3963</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3879</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254">
@@ -6249,16 +6249,16 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>944</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="255">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4103</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="256">
@@ -6295,16 +6295,16 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3222</v>
+        <v>944</v>
       </c>
     </row>
     <row r="257">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="258">
@@ -6341,16 +6341,16 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>587</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="259">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1482</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>21</v>
+        <v>587</v>
       </c>
     </row>
     <row r="261">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6415,11 +6415,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>10</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="262">
@@ -6433,16 +6433,16 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="263">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>283</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>477</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266">
@@ -6525,16 +6525,16 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>547</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="267">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>29</v>
+        <v>283</v>
       </c>
     </row>
     <row r="268">
@@ -6576,11 +6576,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>12</v>
+        <v>547</v>
       </c>
     </row>
     <row r="269">
@@ -6589,21 +6589,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270">
@@ -6612,21 +6612,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>423</v>
+        <v>29</v>
       </c>
     </row>
     <row r="271">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,11 +6645,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>854</v>
+        <v>477</v>
       </c>
     </row>
     <row r="272">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
     </row>
     <row r="273">
@@ -6686,16 +6686,16 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1072</v>
+        <v>423</v>
       </c>
     </row>
     <row r="274">
@@ -6714,11 +6714,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2</v>
+        <v>854</v>
       </c>
     </row>
     <row r="275">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>277</v>
+        <v>106</v>
       </c>
     </row>
     <row r="276">
@@ -6750,21 +6750,21 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>202</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="277">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>468</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>93</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279">
@@ -6824,16 +6824,16 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>434</v>
+        <v>202</v>
       </c>
     </row>
     <row r="280">
@@ -6847,16 +6847,16 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>307</v>
+        <v>468</v>
       </c>
     </row>
     <row r="281">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="282">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>256</v>
+        <v>434</v>
       </c>
     </row>
     <row r="283">
@@ -6916,16 +6916,16 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>343</v>
+        <v>307</v>
       </c>
     </row>
     <row r="284">
@@ -6934,21 +6934,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>115</v>
+        <v>256</v>
       </c>
     </row>
     <row r="286">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4</v>
+        <v>343</v>
       </c>
     </row>
     <row r="287">
@@ -7008,16 +7008,16 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
     </row>
     <row r="288">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>18</v>
+        <v>115</v>
       </c>
     </row>
     <row r="289">
@@ -7049,21 +7049,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>352</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7082,11 +7082,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>60</v>
+        <v>352</v>
       </c>
     </row>
     <row r="293">
@@ -7146,16 +7146,16 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>7</v>
+        <v>317</v>
       </c>
     </row>
     <row r="294">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1674</v>
+        <v>143</v>
       </c>
     </row>
     <row r="295">
@@ -7187,21 +7187,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="296">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7220,11 +7220,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="297">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7266,11 +7266,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="299">
@@ -7284,16 +7284,16 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="300">
@@ -7302,21 +7302,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301">
@@ -7325,21 +7325,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>538</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,11 +7358,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>858</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="304">
@@ -7399,16 +7399,16 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>297</v>
+        <v>110</v>
       </c>
     </row>
     <row r="305">
@@ -7422,16 +7422,16 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>4</v>
+        <v>538</v>
       </c>
     </row>
     <row r="306">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>16</v>
+        <v>858</v>
       </c>
     </row>
     <row r="307">
@@ -7463,21 +7463,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="308">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,11 +7496,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>15</v>
+        <v>297</v>
       </c>
     </row>
     <row r="309">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,11 +7542,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="311">
@@ -7555,21 +7555,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="312">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="314">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="315">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7657,11 +7657,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
     </row>
     <row r="316">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -7716,21 +7716,21 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,11 +7749,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="320">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="321">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>837</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -7808,21 +7808,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="324">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>311</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>544</v>
+        <v>837</v>
       </c>
     </row>
     <row r="326">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="327">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7956,11 +7956,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>290</v>
+        <v>311</v>
       </c>
     </row>
     <row r="329">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>188</v>
+        <v>544</v>
       </c>
     </row>
     <row r="330">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8002,11 +8002,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>318</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8025,11 +8025,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
     </row>
     <row r="332">
@@ -8038,21 +8038,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>8</v>
+        <v>290</v>
       </c>
     </row>
     <row r="333">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>43</v>
+        <v>188</v>
       </c>
     </row>
     <row r="334">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>47</v>
+        <v>318</v>
       </c>
     </row>
     <row r="335">
@@ -8117,11 +8117,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336">
@@ -8135,16 +8135,16 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Terceirizado</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -8163,11 +8163,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="338">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -8186,11 +8186,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>404</v>
+        <v>47</v>
       </c>
     </row>
     <row r="339">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -8209,11 +8209,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>715</v>
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -8222,21 +8222,21 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>7924</v>
+        <v>44</v>
       </c>
     </row>
     <row r="341">
@@ -8255,11 +8255,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>534</v>
+        <v>7</v>
       </c>
     </row>
     <row r="342">
@@ -8278,11 +8278,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>749</v>
+        <v>404</v>
       </c>
     </row>
     <row r="343">
@@ -8296,16 +8296,16 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2006</v>
+        <v>715</v>
       </c>
     </row>
     <row r="344">
@@ -8319,15 +8319,107 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>OUTRAS</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Terceirizado</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TERCEIRIZADO</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
           <t>ESPECIALIZADA</t>
         </is>
       </c>
-      <c r="E344" t="n">
+      <c r="E348" t="n">
         <v>1849</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -1948,16 +1948,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>260</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72">
@@ -2063,16 +2063,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>216</v>
+        <v>37636</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37636</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1598</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3507</v>
+        <v>34063</v>
       </c>
     </row>
     <row r="76">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>34063</v>
+        <v>886</v>
       </c>
     </row>
     <row r="77">
@@ -2178,16 +2178,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>886</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="78">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2334</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="80">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4338</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>22985</v>
+        <v>176905</v>
       </c>
     </row>
     <row r="82">
@@ -2293,16 +2293,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>176905</v>
+        <v>162087</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>162087</v>
+        <v>39786</v>
       </c>
     </row>
     <row r="84">
@@ -2344,11 +2344,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>39786</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="85">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>15695</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>159</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89">
@@ -2454,16 +2454,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>285</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2482,11 +2482,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2495,21 +2495,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>115</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2528,11 +2528,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>83</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -2633,21 +2633,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98">
@@ -2656,21 +2656,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7</v>
+        <v>516</v>
       </c>
     </row>
     <row r="100">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101">
@@ -2725,21 +2725,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>516</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -2771,21 +2771,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="104">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>123</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="105">
@@ -2827,11 +2827,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3052</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108">
@@ -2886,21 +2886,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5200</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>705</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -2965,11 +2965,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>87</v>
+        <v>974</v>
       </c>
     </row>
     <row r="112">
@@ -2978,21 +2978,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>397</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>81</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="114">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3034,11 +3034,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3047,21 +3047,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>974</v>
+        <v>755</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="117">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1356</v>
+        <v>817</v>
       </c>
     </row>
     <row r="118">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="119">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>14404</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1014</v>
+        <v>337</v>
       </c>
     </row>
     <row r="121">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>817</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2690</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="123">
@@ -3231,21 +3231,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>755</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="125">
@@ -3287,11 +3287,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="126">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3310,11 +3310,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>172</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>337</v>
+        <v>250</v>
       </c>
     </row>
     <row r="128">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3356,11 +3356,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129">
@@ -3369,21 +3369,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1208</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130">
@@ -3392,21 +3392,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3415,21 +3415,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="132">
@@ -3438,21 +3438,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1117</v>
+        <v>726</v>
       </c>
     </row>
     <row r="133">
@@ -3461,21 +3461,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>250</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="134">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5</v>
+        <v>701</v>
       </c>
     </row>
     <row r="135">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3517,11 +3517,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>52</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="136">
@@ -3530,21 +3530,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>30</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="137">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="138">
@@ -3576,21 +3576,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>701</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
@@ -3599,21 +3599,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>726</v>
+        <v>140</v>
       </c>
     </row>
     <row r="141">
@@ -3645,21 +3645,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1584</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>10389</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1332</v>
+        <v>54</v>
       </c>
     </row>
     <row r="144">
@@ -3714,21 +3714,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>7508</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>140</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
@@ -3875,21 +3875,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="157">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>85</v>
+        <v>687</v>
       </c>
     </row>
     <row r="161">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>964</v>
       </c>
     </row>
     <row r="162">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2</v>
+        <v>531</v>
       </c>
     </row>
     <row r="163">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="165">
@@ -4197,21 +4197,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>10</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="166">
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4243,21 +4243,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3362</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4276,11 +4276,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>531</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -4312,21 +4312,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>964</v>
+        <v>283</v>
       </c>
     </row>
     <row r="171">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>687</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173">
@@ -4381,21 +4381,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4414,11 +4414,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -4450,17 +4450,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4473,21 +4473,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>283</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="180">
@@ -4542,21 +4542,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="181">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="182">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
@@ -4611,21 +4611,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -4657,21 +4657,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4690,11 +4690,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>64</v>
+        <v>295</v>
       </c>
     </row>
     <row r="187">
@@ -4703,21 +4703,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>92</v>
+        <v>214</v>
       </c>
     </row>
     <row r="188">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>96</v>
+        <v>206</v>
       </c>
     </row>
     <row r="189">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -4772,21 +4772,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="191">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4805,11 +4805,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192">
@@ -4818,21 +4818,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="193">
@@ -4841,21 +4841,21 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>387</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4874,11 +4874,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="195">
@@ -4887,21 +4887,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>206</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>295</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
@@ -4956,21 +4956,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="199">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="201">
@@ -5025,21 +5025,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="202">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5071,21 +5071,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5104,11 +5104,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="205">
@@ -5117,21 +5117,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5209,21 +5209,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210">
@@ -5232,21 +5232,21 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
     </row>
     <row r="211">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="212">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213">
@@ -5301,21 +5301,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="216">
@@ -5370,21 +5370,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="217">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218">
@@ -5416,21 +5416,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>147</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5449,11 +5449,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>104</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="223">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -5554,21 +5554,21 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226">
@@ -5600,21 +5600,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="227">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,11 +5633,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5656,11 +5656,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="229">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,11 +5679,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -5692,21 +5692,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="231">
@@ -5715,21 +5715,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>83</v>
+        <v>113</v>
       </c>
     </row>
     <row r="232">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
     </row>
     <row r="233">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5771,11 +5771,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="235">
@@ -5807,21 +5807,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="236">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5840,11 +5840,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="238">
@@ -5876,21 +5876,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,11 +5909,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>102</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240">
@@ -5922,21 +5922,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>113</v>
+        <v>250</v>
       </c>
     </row>
     <row r="241">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
     </row>
     <row r="242">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>30</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="245">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3</v>
+        <v>944</v>
       </c>
     </row>
     <row r="246">
@@ -6060,21 +6060,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>15</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="247">
@@ -6083,21 +6083,21 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -6106,21 +6106,21 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>268</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="249">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6139,11 +6139,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>250</v>
+        <v>587</v>
       </c>
     </row>
     <row r="250">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>199</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="251">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6185,11 +6185,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3963</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>3879</v>
+        <v>477</v>
       </c>
     </row>
     <row r="256">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>944</v>
+        <v>29</v>
       </c>
     </row>
     <row r="257">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4103</v>
+        <v>283</v>
       </c>
     </row>
     <row r="258">
@@ -6336,21 +6336,21 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3222</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>2</v>
+        <v>547</v>
       </c>
     </row>
     <row r="260">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>587</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="261">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6415,11 +6415,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1482</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="262">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>21</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>854</v>
       </c>
     </row>
     <row r="265">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -6520,21 +6520,21 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5893</v>
+        <v>277</v>
       </c>
     </row>
     <row r="267">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>283</v>
+        <v>93</v>
       </c>
     </row>
     <row r="268">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6576,11 +6576,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>547</v>
+        <v>468</v>
       </c>
     </row>
     <row r="269">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,11 +6599,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>12</v>
+        <v>434</v>
       </c>
     </row>
     <row r="270">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>29</v>
+        <v>256</v>
       </c>
     </row>
     <row r="271">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,11 +6645,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>477</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -6658,21 +6658,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>70</v>
+        <v>202</v>
       </c>
     </row>
     <row r="273">
@@ -6681,21 +6681,21 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>423</v>
+        <v>343</v>
       </c>
     </row>
     <row r="274">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6714,11 +6714,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>854</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275">
@@ -6727,21 +6727,21 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
     </row>
     <row r="276">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1072</v>
+        <v>18</v>
       </c>
     </row>
     <row r="277">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="278">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>277</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
@@ -6819,21 +6819,21 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>202</v>
+        <v>60</v>
       </c>
     </row>
     <row r="280">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6852,11 +6852,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>468</v>
+        <v>25</v>
       </c>
     </row>
     <row r="281">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
     </row>
     <row r="282">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>434</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -6911,21 +6911,21 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>307</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="284">
@@ -6934,21 +6934,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="285">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>256</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>343</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -7003,21 +7003,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>149</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7059,11 +7059,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4</v>
+        <v>858</v>
       </c>
     </row>
     <row r="290">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="292">
@@ -7118,21 +7118,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>352</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>317</v>
+        <v>538</v>
       </c>
     </row>
     <row r="294">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="295">
@@ -7187,21 +7187,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="296">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="297">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="298">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7266,11 +7266,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1674</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299">
@@ -7279,21 +7279,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="304">
@@ -7394,21 +7394,21 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7417,21 +7417,21 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>538</v>
+        <v>66</v>
       </c>
     </row>
     <row r="306">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>858</v>
+        <v>13</v>
       </c>
     </row>
     <row r="307">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7473,11 +7473,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,11 +7496,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>297</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,11 +7519,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>4</v>
+        <v>837</v>
       </c>
     </row>
     <row r="310">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,11 +7542,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="311">
@@ -7555,21 +7555,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>33</v>
+        <v>311</v>
       </c>
     </row>
     <row r="312">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>15</v>
+        <v>544</v>
       </c>
     </row>
     <row r="313">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="315">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>26</v>
+        <v>188</v>
       </c>
     </row>
     <row r="316">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6</v>
+        <v>318</v>
       </c>
     </row>
     <row r="317">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7703,11 +7703,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
     </row>
     <row r="318">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="320">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="322">
@@ -7808,21 +7808,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Terceirizado</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>TERCEIRIZADO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="323">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
     </row>
     <row r="325">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>837</v>
+        <v>715</v>
       </c>
     </row>
     <row r="326">
@@ -7900,21 +7900,21 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>56</v>
+        <v>7924</v>
       </c>
     </row>
     <row r="327">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>8</v>
+        <v>534</v>
       </c>
     </row>
     <row r="328">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7956,11 +7956,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>311</v>
+        <v>749</v>
       </c>
     </row>
     <row r="329">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7979,447 +7979,10 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>3041 - EMATER</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>DIREÇÃO SUPERIOR</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>3051 - EPAMIG</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>3051 - EPAMIG</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>3051 - EPAMIG</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>3051 - EPAMIG</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Terceirizado</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>TERCEIRIZADO</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>DIREÇÃO SUPERIOR</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>DIREÇÃO SUPERIOR</t>
-        </is>
-      </c>
-      <c r="E341" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Inativo</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>INATIVO CIVIL</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>7924</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Terceirizado</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>TERCEIRIZADO</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
         <v>1849</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -481,11 +481,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2733</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -619,11 +619,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>500</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="10">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -660,16 +660,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>830</v>
       </c>
     </row>
     <row r="12">
@@ -688,11 +688,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>565</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -706,16 +706,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>830</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15">
@@ -757,11 +757,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -803,11 +803,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="18">
@@ -826,11 +826,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3652</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="19">
@@ -867,16 +867,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6352</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -895,11 +895,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9150</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="22">
@@ -913,16 +913,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1037</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="23">
@@ -941,11 +941,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1259</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="24">
@@ -964,11 +964,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -987,11 +987,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1097,16 +1097,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1120,16 +1120,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32">
@@ -1148,11 +1148,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36">
@@ -1281,16 +1281,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223</v>
+        <v>468</v>
       </c>
     </row>
     <row r="39">
@@ -1327,16 +1327,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>468</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="42">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>432</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="43">
@@ -1419,16 +1419,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>761</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1260</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1465,16 +1465,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1092</v>
+        <v>761</v>
       </c>
     </row>
     <row r="47">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1335</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -1649,16 +1649,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="55">
@@ -1677,11 +1677,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>750</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="56">
@@ -1695,16 +1695,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4428</v>
+        <v>629</v>
       </c>
     </row>
     <row r="57">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>629</v>
+        <v>750</v>
       </c>
     </row>
     <row r="58">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1213</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60">
@@ -1787,16 +1787,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>430</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61">
@@ -1810,16 +1810,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>109</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62">
@@ -1838,11 +1838,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -1884,11 +1884,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>119</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -1902,16 +1902,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>524</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>41</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67">
@@ -1948,16 +1948,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>524</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>260</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="70">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="71">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>216</v>
+        <v>34063</v>
       </c>
     </row>
     <row r="72">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37636</v>
+        <v>886</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1598</v>
+        <v>37636</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3507</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>34063</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>886</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2334</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>162087</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4338</v>
+        <v>39786</v>
       </c>
     </row>
     <row r="80">
@@ -2247,16 +2247,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>22985</v>
+        <v>176905</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>176905</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>162087</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>39786</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="84">
@@ -2344,11 +2344,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>15695</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>285</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90">
@@ -2477,16 +2477,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92">
@@ -2528,11 +2528,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>200</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>516</v>
       </c>
     </row>
     <row r="97">
@@ -2638,16 +2638,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>88</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -2661,16 +2661,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>516</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>705</v>
       </c>
     </row>
     <row r="102">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>22</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="103">
@@ -2776,16 +2776,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3052</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2822,16 +2822,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>705</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="106">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -2868,16 +2868,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>87</v>
+        <v>397</v>
       </c>
     </row>
     <row r="108">
@@ -2891,16 +2891,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>397</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>974</v>
       </c>
     </row>
     <row r="111">
@@ -2965,11 +2965,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>974</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="113">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1356</v>
+        <v>817</v>
       </c>
     </row>
     <row r="114">
@@ -3029,16 +3029,16 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>755</v>
       </c>
     </row>
     <row r="115">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>755</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1014</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="117">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>817</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>14404</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>337</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>135</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="122">
@@ -3213,16 +3213,16 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="123">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>337</v>
       </c>
     </row>
     <row r="124">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125">
@@ -3287,11 +3287,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>172</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3310,11 +3310,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>250</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -3379,11 +3379,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7</v>
+        <v>250</v>
       </c>
     </row>
     <row r="131">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1584</v>
+        <v>701</v>
       </c>
     </row>
     <row r="134">
@@ -3489,16 +3489,16 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>701</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="135">
@@ -3517,11 +3517,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>10389</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="136">
@@ -3563,11 +3563,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1332</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="138">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139">
@@ -3604,16 +3604,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
@@ -3719,16 +3719,16 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="146">
@@ -3765,16 +3765,16 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="160">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>687</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>531</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>687</v>
       </c>
     </row>
     <row r="164">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>58</v>
+        <v>531</v>
       </c>
     </row>
     <row r="165">
@@ -4225,16 +4225,16 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -4271,16 +4271,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4340,16 +4340,16 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>38</v>
+        <v>283</v>
       </c>
     </row>
     <row r="172">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4478,16 +4478,16 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="184">
@@ -4662,16 +4662,16 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>387</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189">
@@ -4754,16 +4754,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4</v>
+        <v>387</v>
       </c>
     </row>
     <row r="190">
@@ -4805,11 +4805,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
     </row>
     <row r="193">
@@ -4851,11 +4851,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="194">
@@ -4874,11 +4874,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>101</v>
       </c>
     </row>
     <row r="197">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5122,16 +5122,16 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -5168,16 +5168,16 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209">
@@ -5237,16 +5237,16 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>147</v>
+        <v>104</v>
       </c>
     </row>
     <row r="211">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="214">
@@ -5352,16 +5352,16 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
     </row>
     <row r="216">
@@ -5375,16 +5375,16 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218">
@@ -5444,16 +5444,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="220">
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
     </row>
     <row r="223">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="226">
@@ -5909,11 +5909,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="240">
@@ -5932,11 +5932,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>250</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
     </row>
     <row r="244">
@@ -6019,16 +6019,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1482</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="245">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>944</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="246">
@@ -6065,16 +6065,16 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3963</v>
+        <v>944</v>
       </c>
     </row>
     <row r="247">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="248">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3879</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4103</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="251">
@@ -6180,16 +6180,16 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253">
@@ -6249,16 +6249,16 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>477</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>29</v>
+        <v>477</v>
       </c>
     </row>
     <row r="257">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>283</v>
+        <v>547</v>
       </c>
     </row>
     <row r="258">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>547</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260">
@@ -6410,16 +6410,16 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1072</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262">
@@ -6433,16 +6433,16 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>423</v>
+        <v>854</v>
       </c>
     </row>
     <row r="263">
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>854</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="265">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>93</v>
+        <v>468</v>
       </c>
     </row>
     <row r="268">
@@ -6576,11 +6576,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>468</v>
+        <v>93</v>
       </c>
     </row>
     <row r="269">
@@ -6599,11 +6599,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>434</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270">
@@ -6622,11 +6622,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>256</v>
+        <v>434</v>
       </c>
     </row>
     <row r="271">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>202</v>
+        <v>256</v>
       </c>
     </row>
     <row r="273">
@@ -6686,16 +6686,16 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>343</v>
+        <v>202</v>
       </c>
     </row>
     <row r="274">
@@ -6709,16 +6709,16 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
     </row>
     <row r="275">
@@ -6732,16 +6732,16 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>149</v>
+        <v>115</v>
       </c>
     </row>
     <row r="276">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279">
@@ -6824,16 +6824,16 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>60</v>
+        <v>317</v>
       </c>
     </row>
     <row r="280">
@@ -6852,11 +6852,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="281">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
     </row>
     <row r="282">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="283">
@@ -6921,11 +6921,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1674</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -6939,16 +6939,16 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>317</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="285">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -7013,11 +7013,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289">
@@ -7054,16 +7054,16 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>858</v>
+        <v>538</v>
       </c>
     </row>
     <row r="290">
@@ -7082,11 +7082,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4</v>
+        <v>858</v>
       </c>
     </row>
     <row r="291">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="292">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>38</v>
+        <v>297</v>
       </c>
     </row>
     <row r="293">
@@ -7146,16 +7146,16 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>538</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>297</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295">
@@ -7220,11 +7220,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297">
@@ -7266,11 +7266,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="299">
@@ -7289,11 +7289,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="300">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -7358,11 +7358,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="304">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="305">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -481,11 +481,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -619,11 +619,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2733</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -660,16 +660,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>830</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -688,11 +688,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13">
@@ -706,16 +706,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>395</v>
+        <v>830</v>
       </c>
     </row>
     <row r="14">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>565</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -757,11 +757,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -803,11 +803,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -826,11 +826,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1259</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="19">
@@ -867,16 +867,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="21">
@@ -895,11 +895,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3652</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="22">
@@ -913,16 +913,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6352</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="23">
@@ -941,11 +941,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1037</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="24">
@@ -964,11 +964,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -987,11 +987,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1097,16 +1097,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
@@ -1120,16 +1120,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1148,11 +1148,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1281,16 +1281,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>468</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
@@ -1327,16 +1327,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1260</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1335</v>
+        <v>432</v>
       </c>
     </row>
     <row r="43">
@@ -1419,16 +1419,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>432</v>
+        <v>761</v>
       </c>
     </row>
     <row r="45">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46">
@@ -1465,16 +1465,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>761</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="47">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1092</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -1649,16 +1649,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4428</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1677,11 +1677,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1213</v>
+        <v>750</v>
       </c>
     </row>
     <row r="56">
@@ -1695,16 +1695,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>629</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="57">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>750</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="59">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1787,16 +1787,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>78</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61">
@@ -1810,16 +1810,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>430</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62">
@@ -1838,11 +1838,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63">
@@ -1884,11 +1884,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65">
@@ -1902,16 +1902,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>119</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -1948,16 +1948,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>524</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2334</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1598</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3507</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>34063</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>886</v>
+        <v>37636</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37636</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>260</v>
+        <v>34063</v>
       </c>
     </row>
     <row r="76">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>886</v>
       </c>
     </row>
     <row r="77">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>216</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="78">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>162087</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>39786</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="80">
@@ -2247,16 +2247,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>176905</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>15695</v>
+        <v>176905</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4338</v>
+        <v>162087</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>22985</v>
+        <v>39786</v>
       </c>
     </row>
     <row r="84">
@@ -2344,11 +2344,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="85">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2477,16 +2477,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>285</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2528,11 +2528,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93">
@@ -2551,11 +2551,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>516</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>88</v>
+        <v>516</v>
       </c>
     </row>
     <row r="100">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101">
@@ -2730,16 +2730,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>705</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="102">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -2822,16 +2822,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3052</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -2868,16 +2868,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>397</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108">
@@ -2891,16 +2891,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>81</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -2965,11 +2965,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1014</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>817</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="114">
@@ -3029,16 +3029,16 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>755</v>
+        <v>817</v>
       </c>
     </row>
     <row r="115">
@@ -3057,11 +3057,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>14404</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="116">
@@ -3075,16 +3075,16 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1356</v>
+        <v>755</v>
       </c>
     </row>
     <row r="117">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="118">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
     </row>
     <row r="120">
@@ -3167,16 +3167,16 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>189</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="121">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1208</v>
+        <v>337</v>
       </c>
     </row>
     <row r="122">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>337</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="125">
@@ -3287,11 +3287,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3310,11 +3310,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>52</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="129">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>250</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
@@ -3420,16 +3420,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1117</v>
+        <v>52</v>
       </c>
     </row>
     <row r="132">
@@ -3448,11 +3448,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>726</v>
+        <v>701</v>
       </c>
     </row>
     <row r="133">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>701</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="134">
@@ -3489,16 +3489,16 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1584</v>
+        <v>726</v>
       </c>
     </row>
     <row r="135">
@@ -3517,11 +3517,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1332</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="136">
@@ -3535,16 +3535,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>7508</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="137">
@@ -3558,16 +3558,16 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10389</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="138">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
     </row>
     <row r="139">
@@ -3604,16 +3604,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>140</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
@@ -3719,16 +3719,16 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="145">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -3788,16 +3788,16 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="155">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4087,16 +4087,16 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="161">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>964</v>
+        <v>531</v>
       </c>
     </row>
     <row r="162">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>687</v>
+        <v>964</v>
       </c>
     </row>
     <row r="164">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>531</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3362</v>
+        <v>687</v>
       </c>
     </row>
     <row r="166">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
@@ -4271,16 +4271,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -4294,16 +4294,16 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="170">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>283</v>
       </c>
     </row>
     <row r="171">
@@ -4340,16 +4340,16 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>283</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>58</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
@@ -4478,16 +4478,16 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="182">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184">
@@ -4662,16 +4662,16 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="189">
@@ -4754,16 +4754,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>387</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -4805,11 +4805,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="193">
@@ -4851,11 +4851,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -4874,11 +4874,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
     </row>
     <row r="195">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="201">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5122,16 +5122,16 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207">
@@ -5168,16 +5168,16 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5237,16 +5237,16 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>104</v>
+        <v>147</v>
       </c>
     </row>
     <row r="211">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214">
@@ -5352,16 +5352,16 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="216">
@@ -5375,16 +5375,16 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="217">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218">
@@ -5444,16 +5444,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222">
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="223">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226">
@@ -5932,11 +5932,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
     </row>
     <row r="241">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244">
@@ -6019,16 +6019,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3963</v>
+        <v>587</v>
       </c>
     </row>
     <row r="245">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3879</v>
+        <v>944</v>
       </c>
     </row>
     <row r="246">
@@ -6070,11 +6070,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>944</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="247">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4103</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="248">
@@ -6134,16 +6134,16 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>587</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="250">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1482</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="251">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254">
@@ -6254,11 +6254,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6295,16 +6295,16 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>477</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="257">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="259">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260">
@@ -6387,16 +6387,16 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5893</v>
+        <v>477</v>
       </c>
     </row>
     <row r="261">
@@ -6410,16 +6410,16 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>423</v>
+        <v>106</v>
       </c>
     </row>
     <row r="262">
@@ -6438,11 +6438,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>854</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="263">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>106</v>
+        <v>277</v>
       </c>
     </row>
     <row r="264">
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1072</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>854</v>
       </c>
     </row>
     <row r="266">
@@ -6525,16 +6525,16 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>277</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267">
@@ -6599,11 +6599,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>343</v>
+        <v>434</v>
       </c>
     </row>
     <row r="270">
@@ -6622,11 +6622,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>434</v>
+        <v>256</v>
       </c>
     </row>
     <row r="271">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>256</v>
+        <v>202</v>
       </c>
     </row>
     <row r="273">
@@ -6686,16 +6686,16 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>202</v>
+        <v>343</v>
       </c>
     </row>
     <row r="274">
@@ -6709,16 +6709,16 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>149</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
     </row>
     <row r="276">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="277">
@@ -6778,16 +6778,16 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
     </row>
     <row r="278">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
@@ -6824,16 +6824,16 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>317</v>
+        <v>143</v>
       </c>
     </row>
     <row r="280">
@@ -6852,11 +6852,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>143</v>
+        <v>60</v>
       </c>
     </row>
     <row r="281">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="283">
@@ -6916,16 +6916,16 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>7</v>
+        <v>317</v>
       </c>
     </row>
     <row r="284">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="287">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -7054,16 +7054,16 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>538</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>38</v>
+        <v>297</v>
       </c>
     </row>
     <row r="292">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>297</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293">
@@ -7146,16 +7146,16 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4</v>
+        <v>538</v>
       </c>
     </row>
     <row r="294">
@@ -7192,16 +7192,16 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296">
@@ -7220,11 +7220,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="297">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="298">
@@ -7261,16 +7261,16 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
     </row>
     <row r="299">
@@ -7289,11 +7289,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="305">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="306">
@@ -7657,11 +7657,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>188</v>
+        <v>318</v>
       </c>
     </row>
     <row r="316">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>318</v>
+        <v>188</v>
       </c>
     </row>
     <row r="317">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="319">
@@ -7749,11 +7749,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="322">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -444,7 +444,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -458,16 +458,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -504,16 +504,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -522,21 +522,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1259</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -550,16 +550,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2733</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -573,16 +573,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -591,21 +591,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -619,16 +619,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>500</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -646,12 +646,12 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>395</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -660,21 +660,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -688,16 +688,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>565</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -706,21 +706,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>830</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -734,16 +734,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -757,20 +757,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -784,12 +784,12 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>236</v>
+        <v>8775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3652</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -849,16 +849,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>114</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6352</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9150</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1037</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1259</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1014,12 +1014,12 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1028,21 +1028,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1079,16 +1079,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1125,16 +1125,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1148,16 +1148,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,20 +1194,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1240,16 +1240,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>472</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>58</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>312</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1332,16 +1332,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>468</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>791</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1378,16 +1378,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>432</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1401,16 +1401,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19</v>
+        <v>629</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>761</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1447,20 +1447,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1260</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1092</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1493,16 +1493,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1335</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1516,16 +1516,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1580,25 +1580,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1608,20 +1608,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>39</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1654,16 +1654,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>758</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1677,16 +1677,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>750</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4428</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>629</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1746,16 +1746,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1213</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1773,12 +1773,12 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>430</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1838,16 +1838,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1861,16 +1861,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>524</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>41</v>
+        <v>505</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1953,16 +1953,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1976,16 +1976,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1999,16 +1999,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>260</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2022,16 +2022,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2045,16 +2045,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>216</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2068,16 +2068,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37636</v>
+        <v>882</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1598</v>
+        <v>38660</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2114,16 +2114,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3507</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2137,16 +2137,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>34063</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>886</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2183,16 +2183,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2334</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>157263</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2229,16 +2229,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4338</v>
+        <v>39513</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2256,12 +2256,12 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>22985</v>
+        <v>21820</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>176905</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2298,16 +2298,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>162087</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2316,25 +2316,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>39786</v>
+        <v>175689</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2344,16 +2344,16 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>15695</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2362,21 +2362,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2390,16 +2390,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>159</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>285</v>
+        <v>135</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2436,20 +2436,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2459,20 +2459,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2482,16 +2482,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2505,16 +2505,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2546,25 +2546,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>200</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2574,20 +2574,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>112</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2601,12 +2601,12 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2620,16 +2620,16 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>123</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2666,16 +2666,16 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>516</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2712,16 +2712,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>88</v>
+        <v>718</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3052</v>
+        <v>5052</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2758,16 +2758,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>22</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>705</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2845,21 +2845,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>394</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2877,12 +2877,12 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>397</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6</v>
+        <v>962</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2942,20 +2942,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>974</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>87</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2988,16 +2988,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3006,21 +3006,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>14404</v>
+        <v>774</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3034,16 +3034,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>817</v>
+        <v>15944</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3057,16 +3057,16 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1014</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3075,21 +3075,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>755</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3103,20 +3103,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1356</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3126,16 +3126,16 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>135</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1208</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>337</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3218,16 +3218,16 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>172</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3241,16 +3241,16 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>242</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3259,25 +3259,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>189</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3287,16 +3287,16 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3310,16 +3310,16 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3333,16 +3333,16 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3379,16 +3379,16 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3397,25 +3397,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>30</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3425,16 +3425,16 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>52</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>701</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1584</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3489,21 +3489,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>726</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3517,16 +3517,16 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>10389</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1332</v>
+        <v>7446</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7508</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3581,21 +3581,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>140</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3609,16 +3609,16 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -3632,16 +3632,16 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3659,12 +3659,12 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3747,16 +3747,16 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -3770,16 +3770,16 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -3820,12 +3820,12 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3912,12 +3912,12 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3954,16 +3954,16 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3977,20 +3977,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4004,12 +4004,12 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4023,16 +4023,16 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4069,16 +4069,16 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3362</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4115,16 +4115,16 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>531</v>
+        <v>907</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4138,16 +4138,16 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>58</v>
+        <v>528</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4161,16 +4161,16 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>964</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4184,16 +4184,16 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>917</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4202,21 +4202,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>687</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4230,16 +4230,16 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>283</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4345,16 +4345,16 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>58</v>
+        <v>154</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4391,16 +4391,16 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4437,39 +4437,39 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -4483,16 +4483,16 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -4529,39 +4529,39 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -4575,16 +4575,16 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -4593,21 +4593,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -4621,16 +4621,16 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>21</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -4653,30 +4653,30 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>387</v>
+        <v>77</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -4690,16 +4690,16 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>295</v>
+        <v>266</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -4713,16 +4713,16 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>214</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -4736,16 +4736,16 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>206</v>
+        <v>262</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -4759,20 +4759,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4</v>
+        <v>217</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4786,12 +4786,12 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>63</v>
+        <v>391</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -4846,21 +4846,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -4883,30 +4883,30 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -4943,16 +4943,16 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -4966,16 +4966,16 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>51</v>
+        <v>284</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4989,16 +4989,16 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5012,43 +5012,43 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -5076,21 +5076,21 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5104,43 +5104,43 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5150,16 +5150,16 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5196,16 +5196,16 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -5219,43 +5219,43 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>147</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5265,20 +5265,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5288,16 +5288,16 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>23</v>
+        <v>135</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5334,16 +5334,16 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -5357,43 +5357,43 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,20 +5403,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5426,16 +5426,16 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -5472,16 +5472,16 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -5495,20 +5495,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5518,20 +5518,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,20 +5541,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5564,16 +5564,16 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -5587,43 +5587,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,20 +5633,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5656,20 +5656,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,16 +5679,16 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -5697,48 +5697,48 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>102</v>
+        <v>45</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>113</v>
+        <v>35</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5748,20 +5748,20 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5771,20 +5771,20 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,16 +5794,16 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -5840,16 +5840,16 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -5863,43 +5863,43 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>268</v>
+        <v>32</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,20 +5909,20 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>250</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5932,20 +5932,20 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>199</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,16 +5955,16 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -5973,21 +5973,21 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -6001,20 +6001,20 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>165</v>
+        <v>285</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6024,20 +6024,20 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>587</v>
+        <v>229</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6047,20 +6047,20 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>944</v>
+        <v>213</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6070,20 +6070,20 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1482</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3879</v>
+        <v>27</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6116,16 +6116,16 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -6143,12 +6143,12 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>3963</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6162,43 +6162,43 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4103</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>21</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6208,20 +6208,20 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>20</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6254,20 +6254,20 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,43 +6277,43 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>283</v>
+        <v>921</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5893</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6323,20 +6323,20 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>547</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,16 +6369,16 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -6387,25 +6387,25 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>477</v>
+        <v>5636</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6415,20 +6415,20 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>106</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6438,20 +6438,20 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1072</v>
+        <v>251</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>277</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,20 +6484,20 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,16 +6507,16 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>854</v>
+        <v>365</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -6534,16 +6534,16 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,20 +6553,20 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>468</v>
+        <v>906</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,20 +6599,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>434</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6622,20 +6622,20 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,16 +6645,16 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -6672,12 +6672,12 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -6691,20 +6691,20 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>343</v>
+        <v>259</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6718,16 +6718,16 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6737,20 +6737,20 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4</v>
+        <v>518</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6760,43 +6760,43 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>149</v>
+        <v>255</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6806,43 +6806,43 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4</v>
+        <v>668</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6852,20 +6852,20 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6875,20 +6875,20 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,39 +6898,39 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>317</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -6944,20 +6944,20 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1674</v>
+        <v>395</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,20 +6967,20 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,20 +6990,20 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7013,20 +7013,20 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,20 +7036,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7059,20 +7059,20 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7082,20 +7082,20 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>858</v>
+        <v>13</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>297</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7128,16 +7128,16 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -7155,12 +7155,12 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>538</v>
+        <v>573</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>16</v>
+        <v>897</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7201,16 +7201,16 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7220,20 +7220,20 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>9</v>
+        <v>287</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,66 +7243,66 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,20 +7312,20 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,20 +7335,20 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,20 +7358,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,20 +7381,20 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,20 +7404,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7427,20 +7427,20 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,20 +7450,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7473,20 +7473,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,20 +7519,20 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>837</v>
+        <v>14</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,16 +7542,16 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -7565,16 +7565,16 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>311</v>
+        <v>4</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -7588,16 +7588,16 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>544</v>
+        <v>875</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -7611,20 +7611,20 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>8</v>
+        <v>134</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,20 +7634,20 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>112</v>
+        <v>291</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7657,20 +7657,20 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>318</v>
+        <v>508</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7680,16 +7680,16 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>188</v>
+        <v>40</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -7703,20 +7703,20 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>290</v>
+        <v>44</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>43</v>
+        <v>125</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,20 +7749,20 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,16 +7772,16 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -7795,16 +7795,16 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -7818,20 +7818,20 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,20 +7841,20 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7864,20 +7864,20 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>404</v>
+        <v>41</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7891,39 +7891,39 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>715</v>
+        <v>42</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>7924</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,57 +7933,287 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>534</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>4291 - FES</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>749</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
+          <t>4031 - FEPJ</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>MEMBROS DE PODER</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>4031 - FEPJ</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>8775</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>4031 - FEPJ</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>4031 - FEPJ</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
           <t>4291 - FES</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
         <is>
           <t>ESPECIALIZADA</t>
         </is>
       </c>
-      <c r="E329" t="n">
-        <v>1849</v>
+      <c r="E333" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Inativo</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>8189</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>OUTRAS</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>4291 - FES</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="3">
@@ -481,11 +481,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>428</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -522,16 +522,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>266</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -591,16 +591,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -619,11 +619,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2484</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -660,16 +660,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>845</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12">
@@ -683,16 +683,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13">
@@ -711,11 +711,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>660</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -757,11 +757,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16">
@@ -780,11 +780,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8775</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -826,11 +826,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="19">
@@ -849,11 +849,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="20">
@@ -867,16 +867,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3758</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="21">
@@ -890,16 +890,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6862</v>
+        <v>8775</v>
       </c>
     </row>
     <row r="22">
@@ -918,11 +918,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1085</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -941,11 +941,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -964,11 +964,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -982,16 +982,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1033,11 +1033,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
@@ -1074,16 +1074,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
@@ -1097,16 +1097,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -1143,16 +1143,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>311</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
@@ -1281,16 +1281,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39">
@@ -1299,21 +1299,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1306</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40">
@@ -1332,11 +1332,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1105</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="41">
@@ -1350,16 +1350,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>791</v>
+        <v>629</v>
       </c>
     </row>
     <row r="42">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1332</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -1396,16 +1396,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>629</v>
+        <v>791</v>
       </c>
     </row>
     <row r="44">
@@ -1424,11 +1424,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="45">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="47">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1557,16 +1557,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1580,16 +1580,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1535</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>609</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1654,11 +1654,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>758</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="55">
@@ -1677,11 +1677,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>758</v>
       </c>
     </row>
     <row r="56">
@@ -1695,16 +1695,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4380</v>
+        <v>609</v>
       </c>
     </row>
     <row r="57">
@@ -1713,21 +1713,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>157</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="58">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>419</v>
       </c>
     </row>
     <row r="60">
@@ -1787,16 +1787,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>419</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62">
@@ -1838,11 +1838,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -1861,11 +1861,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64">
@@ -1879,16 +1879,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>505</v>
       </c>
     </row>
     <row r="65">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66">
@@ -1925,16 +1925,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>505</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2492</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1798</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3547</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="72">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>882</v>
+        <v>38660</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>38660</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>260</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="76">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>34239</v>
+        <v>882</v>
       </c>
     </row>
     <row r="77">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>14844</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>157263</v>
+        <v>39513</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>39513</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="80">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>21820</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>175689</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4120</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="83">
@@ -2316,16 +2316,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>175689</v>
+        <v>21820</v>
       </c>
     </row>
     <row r="84">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2344,11 +2344,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>74</v>
+        <v>157263</v>
       </c>
     </row>
     <row r="85">
@@ -2362,16 +2362,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>285</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87">
@@ -2413,11 +2413,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -2449,21 +2449,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>132</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90">
@@ -2482,11 +2482,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>57</v>
+        <v>132</v>
       </c>
     </row>
     <row r="92">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96">
@@ -2615,16 +2615,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>294</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>99</v>
+        <v>294</v>
       </c>
     </row>
     <row r="99">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>718</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101">
@@ -2730,16 +2730,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5052</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="102">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>23</v>
+        <v>5052</v>
       </c>
     </row>
     <row r="103">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>718</v>
       </c>
     </row>
     <row r="104">
@@ -2799,16 +2799,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3154</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2827,11 +2827,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106">
@@ -2845,16 +2845,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>394</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
@@ -2896,11 +2896,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>962</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>962</v>
       </c>
     </row>
     <row r="111">
@@ -2955,21 +2955,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1008</v>
+        <v>394</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1016</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="113">
@@ -3006,16 +3006,16 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>774</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -3034,11 +3034,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>15944</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="115">
@@ -3057,11 +3057,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1348</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3</v>
+        <v>15944</v>
       </c>
     </row>
     <row r="117">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>8</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="118">
@@ -3116,21 +3116,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>159</v>
+        <v>774</v>
       </c>
     </row>
     <row r="119">
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>14</v>
+        <v>261</v>
       </c>
     </row>
     <row r="120">
@@ -3167,16 +3167,16 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>68</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="121">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>261</v>
+        <v>68</v>
       </c>
     </row>
     <row r="122">
@@ -3218,11 +3218,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>242</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -3259,16 +3259,16 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1172</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>46</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126">
@@ -3310,11 +3310,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127">
@@ -3328,16 +3328,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>77</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="128">
@@ -3356,11 +3356,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129">
@@ -3379,11 +3379,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>273</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130">
@@ -3397,16 +3397,16 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1058</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3425,11 +3425,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1106</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
@@ -3471,11 +3471,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="134">
@@ -3489,16 +3489,16 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3507,21 +3507,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1116</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="136">
@@ -3576,21 +3576,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>18</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="139">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="144">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>907</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162">
@@ -4156,16 +4156,16 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="164">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>917</v>
+        <v>907</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3286</v>
+        <v>917</v>
       </c>
     </row>
     <row r="166">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168">
@@ -4271,16 +4271,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -4312,21 +4312,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="171">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>154</v>
+        <v>56</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>280</v>
+        <v>154</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>41</v>
+        <v>280</v>
       </c>
     </row>
     <row r="177">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="178">
@@ -4501,16 +4501,16 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4547,16 +4547,16 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="181">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="182">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4616,16 +4616,16 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>281</v>
+        <v>94</v>
       </c>
     </row>
     <row r="184">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="185">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>77</v>
+        <v>281</v>
       </c>
     </row>
     <row r="186">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4690,11 +4690,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>266</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>262</v>
+        <v>217</v>
       </c>
     </row>
     <row r="189">
@@ -4754,16 +4754,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>217</v>
+        <v>391</v>
       </c>
     </row>
     <row r="190">
@@ -4777,16 +4777,16 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>391</v>
+        <v>266</v>
       </c>
     </row>
     <row r="191">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="192">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
     </row>
     <row r="193">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="196">
@@ -4910,21 +4910,21 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>284</v>
+        <v>49</v>
       </c>
     </row>
     <row r="199">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>213</v>
+        <v>24</v>
       </c>
     </row>
     <row r="200">
@@ -5007,16 +5007,16 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="201">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>23</v>
+        <v>213</v>
       </c>
     </row>
     <row r="202">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="203">
@@ -5071,21 +5071,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206">
@@ -5145,16 +5145,16 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="207">
@@ -5163,21 +5163,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="216">
@@ -5380,11 +5380,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
     <row r="217">
@@ -5398,16 +5398,16 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="218">
@@ -5426,11 +5426,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="219">
@@ -5439,21 +5439,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="220">
@@ -5472,11 +5472,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5513,16 +5513,16 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="223">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="224">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -5610,11 +5610,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5656,11 +5656,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="229">
@@ -5679,11 +5679,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="230">
@@ -5692,21 +5692,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="231">
@@ -5725,11 +5725,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="232">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -5766,16 +5766,16 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="234">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>112</v>
+        <v>35</v>
       </c>
     </row>
     <row r="235">
@@ -5807,21 +5807,21 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="236">
@@ -5840,11 +5840,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="238">
@@ -5904,16 +5904,16 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="240">
@@ -5932,11 +5932,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="241">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="242">
@@ -5968,21 +5968,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>169</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>285</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -6024,11 +6024,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>229</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>213</v>
+        <v>99</v>
       </c>
     </row>
     <row r="246">
@@ -6070,11 +6070,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="247">
@@ -6088,16 +6088,16 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>27</v>
+        <v>169</v>
       </c>
     </row>
     <row r="248">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>99</v>
+        <v>229</v>
       </c>
     </row>
     <row r="249">
@@ -6129,21 +6129,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4343</v>
+        <v>213</v>
       </c>
     </row>
     <row r="250">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2772</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6185,11 +6185,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4146</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="252">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4187</v>
+        <v>921</v>
       </c>
     </row>
     <row r="253">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2</v>
+        <v>669</v>
       </c>
     </row>
     <row r="254">
@@ -6249,16 +6249,16 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>669</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="255">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>921</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="256">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="257">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="260">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5636</v>
+        <v>17</v>
       </c>
     </row>
     <row r="261">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>257</v>
+        <v>22</v>
       </c>
     </row>
     <row r="262">
@@ -6438,11 +6438,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>251</v>
+        <v>365</v>
       </c>
     </row>
     <row r="263">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="264">
@@ -6479,16 +6479,16 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>137</v>
+        <v>5636</v>
       </c>
     </row>
     <row r="265">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>365</v>
+        <v>257</v>
       </c>
     </row>
     <row r="266">
@@ -6520,21 +6520,21 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>413</v>
+        <v>251</v>
       </c>
     </row>
     <row r="267">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>906</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -6599,11 +6599,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1205</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6617,16 +6617,16 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2</v>
+        <v>413</v>
       </c>
     </row>
     <row r="271">
@@ -6658,21 +6658,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>205</v>
+        <v>906</v>
       </c>
     </row>
     <row r="273">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6691,11 +6691,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>259</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="274">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>518</v>
+        <v>255</v>
       </c>
     </row>
     <row r="276">
@@ -6778,16 +6778,16 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>255</v>
+        <v>205</v>
       </c>
     </row>
     <row r="278">
@@ -6819,21 +6819,21 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>151</v>
+        <v>518</v>
       </c>
     </row>
     <row r="280">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6852,11 +6852,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="281">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="283">
@@ -6916,16 +6916,16 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>10</v>
+        <v>151</v>
       </c>
     </row>
     <row r="284">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6944,11 +6944,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>395</v>
+        <v>80</v>
       </c>
     </row>
     <row r="285">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1686</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -7013,11 +7013,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>8</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="288">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
     </row>
     <row r="289">
@@ -7049,21 +7049,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2</v>
+        <v>314</v>
       </c>
     </row>
     <row r="290">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7082,11 +7082,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>13</v>
+        <v>180</v>
       </c>
     </row>
     <row r="291">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4</v>
+        <v>395</v>
       </c>
     </row>
     <row r="292">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
@@ -7141,21 +7141,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>573</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>897</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7197,11 +7197,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="298">
@@ -7261,16 +7261,16 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>12</v>
+        <v>573</v>
       </c>
     </row>
     <row r="299">
@@ -7279,21 +7279,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>17</v>
+        <v>897</v>
       </c>
     </row>
     <row r="301">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
@@ -7371,21 +7371,21 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="304">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="306">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="308">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,11 +7496,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="309">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="310">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,11 +7542,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="311">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>134</v>
+        <v>14</v>
       </c>
     </row>
     <row r="314">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>291</v>
+        <v>4</v>
       </c>
     </row>
     <row r="315">
@@ -7657,11 +7657,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>508</v>
+        <v>875</v>
       </c>
     </row>
     <row r="316">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>40</v>
+        <v>134</v>
       </c>
     </row>
     <row r="317">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>44</v>
+        <v>508</v>
       </c>
     </row>
     <row r="318">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>125</v>
+        <v>291</v>
       </c>
     </row>
     <row r="319">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,11 +7749,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="320">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="322">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>42</v>
+        <v>300</v>
       </c>
     </row>
     <row r="323">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="324">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="326">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="327">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>1203</v>
+        <v>42</v>
       </c>
     </row>
     <row r="328">
@@ -7946,21 +7946,21 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6862</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1085</v>
+        <v>498</v>
       </c>
     </row>
     <row r="330">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8002,11 +8002,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>8775</v>
+        <v>383</v>
       </c>
     </row>
     <row r="331">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8025,11 +8025,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332">
@@ -8038,21 +8038,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>4031 - FEPJ</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3758</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="333">
@@ -8071,11 +8071,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>1748</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="334">
@@ -8089,16 +8089,16 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>8189</v>
+        <v>652</v>
       </c>
     </row>
     <row r="335">
@@ -8117,103 +8117,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>DIREÇÃO SUPERIOR</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>7</v>
+        <v>1748</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -481,11 +481,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1245</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>266</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -614,16 +614,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>428</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>226</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11">
@@ -683,16 +683,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>845</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -711,11 +711,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -729,16 +729,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>845</v>
       </c>
     </row>
     <row r="15">
@@ -757,11 +757,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>660</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16">
@@ -780,11 +780,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="17">
@@ -803,11 +803,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1203</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -826,11 +826,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1085</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="19">
@@ -849,11 +849,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3758</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -895,11 +895,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8775</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="22">
@@ -918,11 +918,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>8775</v>
       </c>
     </row>
     <row r="23">
@@ -941,11 +941,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -964,11 +964,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -982,16 +982,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
@@ -1102,11 +1102,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1143,16 +1143,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -1240,11 +1240,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>472</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>54</v>
+        <v>472</v>
       </c>
     </row>
     <row r="38">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>629</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="42">
@@ -1373,16 +1373,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>791</v>
       </c>
     </row>
     <row r="43">
@@ -1396,16 +1396,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>791</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="44">
@@ -1424,11 +1424,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1105</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1332</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -1557,16 +1557,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
@@ -1603,16 +1603,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="54">
@@ -1654,11 +1654,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1535</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55">
@@ -1700,11 +1700,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>609</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>419</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
@@ -1810,16 +1810,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>48</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62">
@@ -1861,11 +1861,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64">
@@ -1879,16 +1879,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>505</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67">
@@ -1948,16 +1948,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>505</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1798</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>260</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="70">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="71">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2492</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="72">
@@ -2063,16 +2063,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>38660</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>882</v>
       </c>
     </row>
     <row r="74">
@@ -2109,16 +2109,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3547</v>
+        <v>38660</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>34239</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>882</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="78">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>39513</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4120</v>
+        <v>157263</v>
       </c>
     </row>
     <row r="80">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>39513</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>175689</v>
+        <v>21820</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>14844</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>21820</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="84">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>157263</v>
+        <v>175689</v>
       </c>
     </row>
     <row r="85">
@@ -2385,16 +2385,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>135</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87">
@@ -2413,11 +2413,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>135</v>
       </c>
     </row>
     <row r="89">
@@ -2454,16 +2454,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -2482,11 +2482,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93">
@@ -2551,11 +2551,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -2569,16 +2569,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95">
@@ -2597,11 +2597,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>294</v>
       </c>
     </row>
     <row r="98">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>294</v>
+        <v>86</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -2730,16 +2730,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3154</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>718</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104">
@@ -2822,16 +2822,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>23</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="106">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -2868,16 +2868,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>394</v>
       </c>
     </row>
     <row r="108">
@@ -2896,11 +2896,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110">
@@ -2960,16 +2960,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>394</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1348</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="113">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>8</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="114">
@@ -3029,16 +3029,16 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1008</v>
+        <v>774</v>
       </c>
     </row>
     <row r="115">
@@ -3057,11 +3057,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>15944</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>15944</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="117">
@@ -3103,11 +3103,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1016</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3121,16 +3121,16 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>774</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3149,11 +3149,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>261</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120">
@@ -3167,16 +3167,16 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1172</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -3218,11 +3218,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>14</v>
+        <v>242</v>
       </c>
     </row>
     <row r="125">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>159</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="126">
@@ -3328,16 +3328,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1058</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -3356,11 +3356,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>273</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129">
@@ -3379,11 +3379,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131">
@@ -3420,16 +3420,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="132">
@@ -3448,11 +3448,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>234</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="133">
@@ -3471,11 +3471,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1106</v>
+        <v>234</v>
       </c>
     </row>
     <row r="134">
@@ -3535,16 +3535,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>7446</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="137">
@@ -3558,16 +3558,16 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10201</v>
+        <v>7446</v>
       </c>
     </row>
     <row r="138">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1116</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="139">
@@ -3604,16 +3604,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -3655,11 +3655,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143">
@@ -3719,16 +3719,16 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="158">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
     </row>
     <row r="162">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>528</v>
+        <v>917</v>
       </c>
     </row>
     <row r="163">
@@ -4156,16 +4156,16 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3286</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164">
@@ -4207,11 +4207,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>917</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -4225,16 +4225,16 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="167">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -4276,11 +4276,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172">
@@ -4363,16 +4363,16 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>56</v>
+        <v>280</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4414,11 +4414,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>280</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>41</v>
+        <v>154</v>
       </c>
     </row>
     <row r="178">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="183">
@@ -4616,16 +4616,16 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="184">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4690,11 +4690,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="187">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>217</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -4754,16 +4754,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>391</v>
+        <v>262</v>
       </c>
     </row>
     <row r="190">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>266</v>
+        <v>217</v>
       </c>
     </row>
     <row r="191">
@@ -4800,16 +4800,16 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>262</v>
+        <v>391</v>
       </c>
     </row>
     <row r="192">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="198">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>49</v>
+        <v>284</v>
       </c>
     </row>
     <row r="199">
@@ -4984,16 +4984,16 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="200">
@@ -5007,16 +5007,16 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>213</v>
+        <v>49</v>
       </c>
     </row>
     <row r="202">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>284</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>23</v>
+        <v>213</v>
       </c>
     </row>
     <row r="204">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="208">
@@ -5214,16 +5214,16 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="215">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="216">
@@ -5380,11 +5380,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5398,16 +5398,16 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>135</v>
+        <v>54</v>
       </c>
     </row>
     <row r="218">
@@ -5426,11 +5426,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="219">
@@ -5444,16 +5444,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
     </row>
     <row r="220">
@@ -5467,16 +5467,16 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="221">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222">
@@ -5513,16 +5513,16 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223">
@@ -5541,11 +5541,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226">
@@ -5610,11 +5610,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="227">
@@ -5633,11 +5633,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="228">
@@ -5656,11 +5656,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
@@ -5720,16 +5720,16 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="232">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="233">
@@ -5766,16 +5766,16 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="234">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -5835,16 +5835,16 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="237">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="238">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -5904,16 +5904,16 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>116</v>
+        <v>32</v>
       </c>
     </row>
     <row r="240">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="243">
@@ -5996,16 +5996,16 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="244">
@@ -6024,11 +6024,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>285</v>
+        <v>213</v>
       </c>
     </row>
     <row r="245">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>99</v>
+        <v>285</v>
       </c>
     </row>
     <row r="246">
@@ -6088,16 +6088,16 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>169</v>
+        <v>99</v>
       </c>
     </row>
     <row r="248">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>229</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -6139,11 +6139,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="250">
@@ -6157,16 +6157,16 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="251">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>921</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="253">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>669</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="254">
@@ -6249,16 +6249,16 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4343</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4146</v>
+        <v>669</v>
       </c>
     </row>
     <row r="256">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4187</v>
+        <v>921</v>
       </c>
     </row>
     <row r="257">
@@ -6318,16 +6318,16 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="258">
@@ -6392,11 +6392,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -6410,16 +6410,16 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="262">
@@ -6433,16 +6433,16 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>365</v>
+        <v>5636</v>
       </c>
     </row>
     <row r="263">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>137</v>
+        <v>257</v>
       </c>
     </row>
     <row r="264">
@@ -6479,16 +6479,16 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5636</v>
+        <v>251</v>
       </c>
     </row>
     <row r="265">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>257</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -6530,11 +6530,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>251</v>
+        <v>137</v>
       </c>
     </row>
     <row r="267">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
     </row>
     <row r="268">
@@ -6571,16 +6571,16 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>63</v>
+        <v>413</v>
       </c>
     </row>
     <row r="269">
@@ -6599,11 +6599,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>2</v>
+        <v>906</v>
       </c>
     </row>
     <row r="270">
@@ -6617,16 +6617,16 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>413</v>
+        <v>63</v>
       </c>
     </row>
     <row r="271">
@@ -6645,11 +6645,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>308</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="272">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>906</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -6691,11 +6691,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1205</v>
+        <v>308</v>
       </c>
     </row>
     <row r="274">
@@ -6709,16 +6709,16 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>66</v>
+        <v>205</v>
       </c>
     </row>
     <row r="275">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="276">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="277">
@@ -6778,16 +6778,16 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>205</v>
+        <v>518</v>
       </c>
     </row>
     <row r="278">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>668</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -6829,11 +6829,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>518</v>
+        <v>255</v>
       </c>
     </row>
     <row r="280">
@@ -6852,11 +6852,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>259</v>
+        <v>668</v>
       </c>
     </row>
     <row r="281">
@@ -6870,16 +6870,16 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>10</v>
+        <v>151</v>
       </c>
     </row>
     <row r="282">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="283">
@@ -6916,16 +6916,16 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>151</v>
+        <v>33</v>
       </c>
     </row>
     <row r="284">
@@ -6944,11 +6944,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286">
@@ -6985,16 +6985,16 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>8</v>
+        <v>314</v>
       </c>
     </row>
     <row r="287">
@@ -7013,11 +7013,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1686</v>
+        <v>395</v>
       </c>
     </row>
     <row r="288">
@@ -7054,16 +7054,16 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>314</v>
+        <v>180</v>
       </c>
     </row>
     <row r="290">
@@ -7082,11 +7082,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>395</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="292">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
@@ -7197,11 +7197,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
@@ -7215,16 +7215,16 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>287</v>
+        <v>573</v>
       </c>
     </row>
     <row r="297">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>34</v>
+        <v>897</v>
       </c>
     </row>
     <row r="298">
@@ -7261,16 +7261,16 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>573</v>
+        <v>34</v>
       </c>
     </row>
     <row r="299">
@@ -7289,11 +7289,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>12</v>
+        <v>287</v>
       </c>
     </row>
     <row r="300">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>897</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="302">
@@ -7353,16 +7353,16 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="303">
@@ -7376,16 +7376,16 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="304">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
     </row>
     <row r="306">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="307">
@@ -7496,11 +7496,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -7519,11 +7519,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="310">
@@ -7542,11 +7542,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="311">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="313">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7703,11 +7703,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>508</v>
+        <v>291</v>
       </c>
     </row>
     <row r="318">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>291</v>
+        <v>508</v>
       </c>
     </row>
     <row r="319">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>191</v>
+        <v>44</v>
       </c>
     </row>
     <row r="321">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
     </row>
     <row r="322">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="324">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="325">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="326">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="328">
@@ -7956,11 +7956,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="329">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>498</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -8025,11 +8025,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>7</v>
+        <v>652</v>
       </c>
     </row>
     <row r="332">
@@ -8071,11 +8071,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2426</v>
+        <v>498</v>
       </c>
     </row>
     <row r="334">
@@ -8094,11 +8094,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>652</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="335">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -3908,11 +3908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="157">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>528</v>
+        <v>917</v>
       </c>
     </row>
     <row r="162">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>917</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>75</v>
+        <v>907</v>
       </c>
     </row>
     <row r="164">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>907</v>
+        <v>528</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="166">
@@ -4225,16 +4225,16 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3286</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -4248,16 +4248,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="168">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="180">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>94</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="184">
@@ -4639,16 +4639,16 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>281</v>
+        <v>94</v>
       </c>
     </row>
     <row r="185">
@@ -4690,11 +4690,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="189">
@@ -4759,11 +4759,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>262</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -4874,11 +4874,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="196">
@@ -4938,16 +4938,16 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="198">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>284</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -4984,16 +4984,16 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="200">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>284</v>
       </c>
     </row>
     <row r="201">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>23</v>
+        <v>213</v>
       </c>
     </row>
     <row r="203">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>213</v>
+        <v>24</v>
       </c>
     </row>
     <row r="204">
@@ -5099,16 +5099,16 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="205">
@@ -5145,16 +5145,16 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -5214,16 +5214,16 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -5283,16 +5283,16 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="214">
@@ -5329,16 +5329,16 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
     </row>
     <row r="215">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="216">
@@ -5380,11 +5380,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="217">
@@ -5426,11 +5426,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -5444,16 +5444,16 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>135</v>
+        <v>48</v>
       </c>
     </row>
     <row r="220">
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223">
@@ -5587,11 +5587,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="226">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283">
@@ -6921,11 +6921,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="284">
@@ -6944,11 +6944,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="285">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -1332,11 +1332,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1306</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="41">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1105</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="42">
@@ -1373,16 +1373,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>791</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -1396,16 +1396,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1332</v>
+        <v>791</v>
       </c>
     </row>
     <row r="44">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="47">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -1557,16 +1557,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
@@ -1603,16 +1603,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1672,16 +1672,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>758</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="56">
@@ -1718,16 +1718,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4380</v>
+        <v>758</v>
       </c>
     </row>
     <row r="58">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4133,16 +4133,16 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>75</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="163">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>528</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3286</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166">
@@ -4230,11 +4230,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>528</v>
       </c>
     </row>
     <row r="167">
@@ -4276,11 +4276,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -4322,11 +4322,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>41</v>
+        <v>154</v>
       </c>
     </row>
     <row r="172">
@@ -4363,16 +4363,16 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>280</v>
+        <v>41</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="174">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4501,16 +4501,16 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="179">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4547,16 +4547,16 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="186">
@@ -4708,16 +4708,16 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>262</v>
+        <v>391</v>
       </c>
     </row>
     <row r="188">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>217</v>
+        <v>262</v>
       </c>
     </row>
     <row r="191">
@@ -4800,16 +4800,16 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>391</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="199">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>49</v>
+        <v>284</v>
       </c>
     </row>
     <row r="200">
@@ -5012,11 +5012,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>284</v>
+        <v>213</v>
       </c>
     </row>
     <row r="201">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>213</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="208">
@@ -5191,16 +5191,16 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
@@ -5219,11 +5219,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211">
@@ -5283,16 +5283,16 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214">
@@ -5380,11 +5380,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="217">
@@ -5449,11 +5449,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="220">
@@ -6185,11 +6185,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2772</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="252">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4146</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="253">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4187</v>
+        <v>669</v>
       </c>
     </row>
     <row r="254">
@@ -6254,11 +6254,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2</v>
+        <v>921</v>
       </c>
     </row>
     <row r="255">
@@ -6277,11 +6277,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>669</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>921</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="257">
@@ -6898,11 +6898,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="283">
@@ -6921,11 +6921,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="284">
@@ -6944,11 +6944,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6967,11 +6967,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -7151,11 +7151,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7174,11 +7174,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="295">
@@ -7197,11 +7197,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>897</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298">
@@ -7266,11 +7266,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>34</v>
+        <v>897</v>
       </c>
     </row>
     <row r="299">
@@ -7289,11 +7289,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>287</v>
+        <v>4</v>
       </c>
     </row>
     <row r="300">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="301">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>12</v>
+        <v>287</v>
       </c>
     </row>
     <row r="302">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
     </row>
     <row r="321">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
     </row>
     <row r="322">
@@ -7818,11 +7818,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>300</v>
+        <v>44</v>
       </c>
     </row>
     <row r="323">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="326">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="328">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -444,7 +444,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -458,16 +458,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2484</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -504,16 +504,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>428</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -522,21 +522,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -550,16 +550,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>266</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -573,16 +573,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -596,16 +596,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -614,21 +614,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1245</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>660</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -665,16 +665,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -729,21 +729,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>845</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -780,16 +780,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3758</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -844,21 +844,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6862</v>
+        <v>8557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1085</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -918,16 +918,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8775</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1083,12 +1083,12 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1102,16 +1102,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1129,12 +1129,12 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,16 +1194,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>54</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>472</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1286,39 +1286,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>311</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1332,16 +1332,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1306</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1105</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>791</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1401,16 +1401,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1332</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1424,20 +1424,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>629</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1470,16 +1470,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1516,16 +1516,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,39 +1585,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>767</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1626,21 +1626,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1535</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1658,12 +1658,12 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>609</v>
+        <v>570</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>758</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1727,12 +1727,12 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4380</v>
+        <v>409</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1750,12 +1750,12 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1796,35 +1796,35 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>419</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1861,16 +1861,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1893,11 +1893,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1911,16 +1911,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1934,35 +1934,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>118</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>505</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1980,12 +1980,12 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2492</v>
+        <v>39337</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2026,12 +2026,12 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1798</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2049,12 +2049,12 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3547</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2068,16 +2068,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>33828</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2095,12 +2095,12 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>882</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2109,25 +2109,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>38660</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>260</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2183,16 +2183,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34239</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2201,21 +2201,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>14844</v>
+        <v>176055</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>157263</v>
+        <v>158968</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2256,12 +2256,12 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>39513</v>
+        <v>37607</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2275,20 +2275,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>21820</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4120</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2348,12 +2348,12 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>175689</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2371,12 +2371,12 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>285</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2436,20 +2436,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2459,16 +2459,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2477,21 +2477,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2509,12 +2509,12 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2528,20 +2528,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>57</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2555,35 +2555,35 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2689,39 +2689,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2735,16 +2735,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>718</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2758,20 +2758,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5052</v>
+        <v>724</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2804,20 +2804,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3154</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2850,16 +2850,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2868,21 +2868,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>394</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2896,20 +2896,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>983</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2919,20 +2919,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2942,20 +2942,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>962</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2988,16 +2988,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1008</v>
+        <v>17855</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3011,16 +3011,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1016</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>774</v>
+        <v>804</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>15944</v>
+        <v>830</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1348</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3103,20 +3103,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3126,16 +3126,16 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3172,16 +3172,16 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3218,20 +3218,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>261</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3241,20 +3241,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3264,20 +3264,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>242</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3291,12 +3291,12 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1172</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3333,43 +3333,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>77</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3379,20 +3379,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>751</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3402,66 +3402,66 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>273</v>
+        <v>624</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1058</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1106</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3471,20 +3471,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>234</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3494,43 +3494,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1571</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3540,89 +3540,89 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1116</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7446</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>10201</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3632,20 +3632,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3655,43 +3655,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,20 +3701,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3724,43 +3724,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,20 +3793,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,20 +3816,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3839,20 +3839,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -3871,11 +3871,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3912,16 +3912,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3935,16 +3935,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3954,20 +3954,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3977,20 +3977,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,20 +4000,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,20 +4023,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4046,20 +4046,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4069,20 +4069,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,16 +4092,16 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>61</v>
+        <v>807</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>917</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4138,20 +4138,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>75</v>
+        <v>916</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4161,66 +4161,66 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>907</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>528</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3286</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4234,62 +4234,62 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13</v>
+        <v>281</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4299,20 +4299,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4322,16 +4322,16 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4345,16 +4345,16 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>280</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4391,20 +4391,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4414,20 +4414,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4437,43 +4437,43 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4483,20 +4483,20 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4506,66 +4506,66 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4579,12 +4579,12 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -4598,20 +4598,20 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4621,43 +4621,43 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>94</v>
+        <v>266</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4667,39 +4667,39 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>262</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>77</v>
+        <v>391</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -4713,20 +4713,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>262</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,20 +4736,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>266</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4759,20 +4759,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4786,35 +4786,35 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>217</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>391</v>
+        <v>109</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -4823,25 +4823,25 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4855,16 +4855,16 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4874,20 +4874,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4897,20 +4897,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4920,16 +4920,16 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -4938,21 +4938,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -4966,16 +4966,16 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4989,20 +4989,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>49</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5012,20 +5012,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>284</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5035,43 +5035,43 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5081,43 +5081,43 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5131,39 +5131,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5177,12 +5177,12 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5196,20 +5196,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5219,20 +5219,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5242,66 +5242,66 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5311,16 +5311,16 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5329,48 +5329,48 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5380,20 +5380,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,20 +5403,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5435,11 +5435,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5449,16 +5449,16 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -5467,25 +5467,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5499,16 +5499,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5522,16 +5522,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5545,16 +5545,16 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5564,43 +5564,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5614,16 +5614,16 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,20 +5633,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5656,20 +5656,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,20 +5679,20 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5702,20 +5702,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5729,16 +5729,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,16 +5752,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5775,16 +5775,16 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,20 +5794,20 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5817,16 +5817,16 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -5835,48 +5835,48 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>80</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5886,20 +5886,20 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>32</v>
+        <v>202</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,20 +5909,20 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>32</v>
+        <v>284</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5932,20 +5932,20 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,20 +5955,20 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5978,16 +5978,16 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -5996,48 +5996,48 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>169</v>
+        <v>239</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>213</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6047,20 +6047,20 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>285</v>
+        <v>5571</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6070,20 +6070,20 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>27</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>99</v>
+        <v>633</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6116,20 +6116,20 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>291</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6139,16 +6139,16 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>229</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6157,48 +6157,48 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4343</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2772</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6208,20 +6208,20 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4146</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4187</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6258,16 +6258,16 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,66 +6277,66 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>669</v>
+        <v>16</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>921</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>22</v>
+        <v>161</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,20 +6369,20 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6392,20 +6392,20 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3</v>
+        <v>199</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6419,16 +6419,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>17</v>
+        <v>421</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6442,16 +6442,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5636</v>
+        <v>455</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>257</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,20 +6484,20 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>251</v>
+        <v>63</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,20 +6507,20 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6530,20 +6530,20 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,20 +6553,20 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>413</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,20 +6599,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>906</v>
+        <v>281</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6622,20 +6622,20 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,20 +6645,20 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1205</v>
+        <v>722</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6691,16 +6691,16 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>308</v>
+        <v>229</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -6709,48 +6709,48 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205</v>
+        <v>307</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>259</v>
+        <v>147</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,20 +6783,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>518</v>
+        <v>22</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6829,66 +6829,66 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>255</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>668</v>
+        <v>323</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>151</v>
+        <v>384</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,20 +6898,20 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>80</v>
+        <v>183</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6944,20 +6944,20 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,43 +6967,43 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>314</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7013,20 +7013,20 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,20 +7036,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7063,39 +7063,39 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>8</v>
+        <v>585</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1686</v>
+        <v>909</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7128,20 +7128,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7151,20 +7151,20 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>13</v>
+        <v>335</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7183,11 +7183,11 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7197,20 +7197,20 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7224,16 +7224,16 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>573</v>
+        <v>32</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,20 +7243,20 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>897</v>
+        <v>17</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7266,20 +7266,20 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7293,16 +7293,16 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>287</v>
+        <v>83</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,20 +7312,20 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,43 +7335,43 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7385,16 +7385,16 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,20 +7404,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7427,20 +7427,20 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,20 +7450,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7473,20 +7473,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,20 +7496,20 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,20 +7519,20 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,20 +7542,20 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,43 +7565,43 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3</v>
+        <v>887</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,16 +7611,16 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -7634,16 +7634,16 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -7657,16 +7657,16 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>875</v>
+        <v>448</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -7680,20 +7680,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>134</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7703,20 +7703,20 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>291</v>
+        <v>44</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>508</v>
+        <v>189</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,16 +7749,16 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -7772,20 +7772,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>44</v>
+        <v>291</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,20 +7795,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7818,20 +7818,20 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,16 +7841,16 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>191</v>
+        <v>56</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -7887,20 +7887,20 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7910,20 +7910,20 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,20 +7933,20 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7960,12 +7960,12 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>42</v>
+        <v>250</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -7974,21 +7974,21 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>7</v>
+        <v>8614</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -8002,16 +8002,16 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>383</v>
+        <v>949</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>652</v>
+        <v>449</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -8043,85 +8043,16 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>8189</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>1748</v>
+        <v>1925</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -444,7 +444,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -458,16 +458,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2484</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -504,16 +504,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>428</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -522,21 +522,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -550,16 +550,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>266</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -573,16 +573,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -596,16 +596,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -614,21 +614,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1245</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>660</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -665,16 +665,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -729,21 +729,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>845</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -780,16 +780,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3758</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -844,21 +844,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6862</v>
+        <v>8557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1085</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -918,16 +918,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8775</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1083,12 +1083,12 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1102,16 +1102,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1129,12 +1129,12 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,16 +1194,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>54</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>472</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1286,39 +1286,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>311</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1332,16 +1332,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1332</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1306</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1378,16 +1378,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>791</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1424,20 +1424,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>629</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>1101 - OGE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1470,16 +1470,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1105</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1516,16 +1516,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1557,25 +1557,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,20 +1585,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1608,16 +1608,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>767</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1626,21 +1626,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1535</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1658,12 +1658,12 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>609</v>
+        <v>570</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1672,25 +1672,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4380</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1704,35 +1704,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>758</v>
+        <v>409</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1750,12 +1750,12 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1796,35 +1796,35 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>419</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1861,16 +1861,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1893,11 +1893,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1911,16 +1911,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1934,35 +1934,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>118</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>505</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1980,12 +1980,12 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2492</v>
+        <v>39337</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2026,12 +2026,12 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1798</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2049,12 +2049,12 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3547</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2068,16 +2068,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>33828</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2095,12 +2095,12 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>882</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2109,25 +2109,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>38660</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>260</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2183,16 +2183,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34239</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2201,21 +2201,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>14844</v>
+        <v>176055</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>157263</v>
+        <v>158968</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2256,12 +2256,12 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>39513</v>
+        <v>37607</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2275,20 +2275,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>21820</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4120</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2348,12 +2348,12 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>175689</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2371,12 +2371,12 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>285</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2436,20 +2436,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2459,16 +2459,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2477,21 +2477,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2509,12 +2509,12 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2528,20 +2528,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>57</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2555,35 +2555,35 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2689,39 +2689,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2735,16 +2735,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>718</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2758,20 +2758,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5052</v>
+        <v>724</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2804,20 +2804,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3154</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2850,16 +2850,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2868,21 +2868,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>394</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2896,20 +2896,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>983</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2919,20 +2919,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2942,20 +2942,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>962</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2988,16 +2988,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1008</v>
+        <v>17855</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3011,16 +3011,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1016</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>774</v>
+        <v>804</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>15944</v>
+        <v>830</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1348</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3103,20 +3103,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3126,16 +3126,16 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3172,16 +3172,16 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3195,16 +3195,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3218,20 +3218,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>261</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3241,20 +3241,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3264,20 +3264,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>242</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3291,12 +3291,12 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1172</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3333,43 +3333,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>77</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3379,20 +3379,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>751</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3402,66 +3402,66 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>273</v>
+        <v>624</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1058</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1106</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3471,20 +3471,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>234</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3494,43 +3494,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1571</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3540,89 +3540,89 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1116</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7446</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>10201</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3632,20 +3632,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3655,43 +3655,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1541 - ESP MG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3701,20 +3701,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3724,43 +3724,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,20 +3793,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,20 +3816,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3839,20 +3839,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -3871,11 +3871,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3908,20 +3908,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3977,20 +3977,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,20 +4000,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,20 +4023,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4046,20 +4046,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,16 +4092,16 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>61</v>
+        <v>807</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>917</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3286</v>
+        <v>916</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4161,43 +4161,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>907</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4207,20 +4207,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4230,66 +4230,66 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>528</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4299,20 +4299,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>148</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4322,16 +4322,16 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4345,16 +4345,16 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4391,43 +4391,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>280</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4437,43 +4437,43 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4483,66 +4483,66 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>14</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4552,20 +4552,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4579,12 +4579,12 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -4607,11 +4607,11 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4621,43 +4621,43 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>281</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>94</v>
+        <v>266</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4667,39 +4667,39 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53</v>
+        <v>262</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>77</v>
+        <v>391</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -4708,25 +4708,25 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>391</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,20 +4736,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>266</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4759,20 +4759,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4782,20 +4782,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4805,16 +4805,16 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>217</v>
+        <v>109</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -4823,71 +4823,71 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4897,20 +4897,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4920,16 +4920,16 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -4938,21 +4938,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -4966,16 +4966,16 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>49</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>284</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5012,20 +5012,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>213</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5035,43 +5035,43 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>2161 - FUCAM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5081,43 +5081,43 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5127,43 +5127,43 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>2171 - FAOP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5173,16 +5173,16 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5191,25 +5191,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5219,20 +5219,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5242,43 +5242,43 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>25</v>
+        <v>102</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5288,20 +5288,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5311,16 +5311,16 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5329,48 +5329,48 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5380,20 +5380,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5403,20 +5403,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5435,11 +5435,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5449,16 +5449,16 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -5467,25 +5467,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5499,16 +5499,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5522,16 +5522,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5545,16 +5545,16 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2211 - TV MINAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5564,43 +5564,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5614,16 +5614,16 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,20 +5633,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5656,20 +5656,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5679,20 +5679,20 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5702,20 +5702,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5729,16 +5729,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,16 +5752,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5775,16 +5775,16 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5794,20 +5794,20 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5817,16 +5817,16 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -5835,48 +5835,48 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>80</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5886,20 +5886,20 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>32</v>
+        <v>202</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,20 +5909,20 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>32</v>
+        <v>284</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5932,20 +5932,20 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,20 +5955,20 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5978,16 +5978,16 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -5996,48 +5996,48 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>169</v>
+        <v>239</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>213</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6047,20 +6047,20 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>285</v>
+        <v>5571</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6070,20 +6070,20 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>27</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>99</v>
+        <v>633</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6116,20 +6116,20 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>291</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6139,16 +6139,16 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>229</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6157,48 +6157,48 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4343</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4187</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6208,20 +6208,20 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2772</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6235,16 +6235,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>669</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6254,20 +6254,20 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,66 +6277,66 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4146</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>22</v>
+        <v>161</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,20 +6369,20 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6392,20 +6392,20 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3</v>
+        <v>199</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6419,16 +6419,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>17</v>
+        <v>421</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6442,16 +6442,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5636</v>
+        <v>455</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>257</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,20 +6484,20 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>251</v>
+        <v>63</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,20 +6507,20 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6530,20 +6530,20 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,20 +6553,20 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>413</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,20 +6599,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>906</v>
+        <v>281</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6622,20 +6622,20 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,20 +6645,20 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1205</v>
+        <v>722</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6691,16 +6691,16 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>308</v>
+        <v>229</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -6709,48 +6709,48 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205</v>
+        <v>307</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>259</v>
+        <v>147</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,20 +6783,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>518</v>
+        <v>22</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6829,66 +6829,66 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>255</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>668</v>
+        <v>323</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>151</v>
+        <v>384</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6898,20 +6898,20 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>33</v>
+        <v>183</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6948,16 +6948,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,43 +6967,43 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>10</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>314</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7013,20 +7013,20 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,20 +7036,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7063,39 +7063,39 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>8</v>
+        <v>585</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1686</v>
+        <v>909</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7128,20 +7128,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7151,20 +7151,20 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2</v>
+        <v>335</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7197,20 +7197,20 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7224,16 +7224,16 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>573</v>
+        <v>32</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,20 +7243,20 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7266,20 +7266,20 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>897</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7289,20 +7289,20 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,20 +7312,20 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,43 +7335,43 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>287</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7385,16 +7385,16 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,20 +7404,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7427,20 +7427,20 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7450,20 +7450,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7473,20 +7473,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,20 +7496,20 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,20 +7519,20 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,20 +7542,20 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,43 +7565,43 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3</v>
+        <v>887</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,16 +7611,16 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -7634,16 +7634,16 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -7657,16 +7657,16 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>875</v>
+        <v>448</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -7680,20 +7680,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>134</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7703,20 +7703,20 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>291</v>
+        <v>44</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>508</v>
+        <v>189</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,16 +7749,16 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -7772,20 +7772,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>125</v>
+        <v>291</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,20 +7795,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>300</v>
+        <v>16</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7818,20 +7818,20 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7841,16 +7841,16 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>191</v>
+        <v>56</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -7887,20 +7887,20 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7914,16 +7914,16 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7933,20 +7933,20 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7960,12 +7960,12 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>42</v>
+        <v>250</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -7974,21 +7974,21 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>7</v>
+        <v>8614</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -8002,16 +8002,16 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>383</v>
+        <v>949</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>652</v>
+        <v>449</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -8043,85 +8043,16 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>8189</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>1748</v>
+        <v>1925</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="4">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>295</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1251</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2466</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>429</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11">
@@ -665,11 +665,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>667</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12">
@@ -711,11 +711,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -821,16 +821,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6977</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -1097,16 +1097,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1120,16 +1120,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -1143,16 +1143,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35">
@@ -1212,16 +1212,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36">
@@ -1235,16 +1235,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>319</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -1286,11 +1286,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>434</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="40">
@@ -1332,11 +1332,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>778</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="41">
@@ -1350,16 +1350,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>483</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="42">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1365</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1086</v>
+        <v>778</v>
       </c>
     </row>
     <row r="44">
@@ -1419,16 +1419,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1483</v>
+        <v>483</v>
       </c>
     </row>
     <row r="45">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
@@ -1488,16 +1488,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1557,16 +1557,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="52">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>767</v>
+        <v>570</v>
       </c>
     </row>
     <row r="53">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4293</v>
+        <v>767</v>
       </c>
     </row>
     <row r="54">
@@ -1654,11 +1654,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>570</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1672,16 +1672,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="56">
@@ -1700,11 +1700,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57">
@@ -1718,16 +1718,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>409</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>133</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46</v>
+        <v>409</v>
       </c>
     </row>
     <row r="60">
@@ -1792,11 +1792,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -1810,16 +1810,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>108</v>
+        <v>481</v>
       </c>
     </row>
     <row r="62">
@@ -1833,16 +1833,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>481</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -1861,11 +1861,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64">
@@ -1884,11 +1884,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>237</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="67">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>190</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="69">
@@ -1994,16 +1994,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2017,16 +2017,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1793</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71">
@@ -2040,16 +2040,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3764</v>
+        <v>39337</v>
       </c>
     </row>
     <row r="72">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>33828</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>470</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2339</v>
+        <v>33828</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="76">
@@ -2160,11 +2160,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4144</v>
+        <v>158968</v>
       </c>
     </row>
     <row r="77">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>23323</v>
+        <v>37607</v>
       </c>
     </row>
     <row r="78">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>176055</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>158968</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>37607</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14014</v>
+        <v>176055</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>276</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90">
@@ -2477,16 +2477,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>89</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>21</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>333</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>724</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="100">
@@ -2707,16 +2707,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3219</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5145</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>724</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="103">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>285</v>
+        <v>17855</v>
       </c>
     </row>
     <row r="111">
@@ -2960,16 +2960,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>830</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>17855</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>830</v>
+        <v>285</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>287</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>142</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119">
@@ -3144,16 +3144,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1151</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="122">
@@ -3218,11 +3218,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>147</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>262</v>
+        <v>46</v>
       </c>
     </row>
     <row r="124">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>63</v>
+        <v>262</v>
       </c>
     </row>
     <row r="125">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1073</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126">
@@ -3305,16 +3305,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>46</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="127">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1589</v>
+        <v>624</v>
       </c>
     </row>
     <row r="129">
@@ -3374,16 +3374,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>751</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="130">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>624</v>
+        <v>751</v>
       </c>
     </row>
     <row r="131">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="135">
@@ -3535,16 +3535,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3650,16 +3650,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144">
@@ -3724,11 +3724,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="156">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4041,16 +4041,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="159">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>807</v>
+        <v>916</v>
       </c>
     </row>
     <row r="161">
@@ -4110,16 +4110,16 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3346</v>
+        <v>807</v>
       </c>
     </row>
     <row r="162">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>916</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4179,16 +4179,16 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166">
@@ -4230,11 +4230,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
@@ -4248,16 +4248,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>43</v>
+        <v>281</v>
       </c>
     </row>
     <row r="168">
@@ -4271,16 +4271,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>148</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>148</v>
       </c>
     </row>
     <row r="174">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="177">
@@ -4501,16 +4501,16 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>296</v>
+        <v>95</v>
       </c>
     </row>
     <row r="179">
@@ -4524,16 +4524,16 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="180">
@@ -4552,11 +4552,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="181">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>296</v>
       </c>
     </row>
     <row r="183">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>217</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="185">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="186">
@@ -4685,16 +4685,16 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>391</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187">
@@ -4708,16 +4708,16 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>391</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4</v>
+        <v>109</v>
       </c>
     </row>
     <row r="189">
@@ -4759,11 +4759,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
@@ -4800,16 +4800,16 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
     </row>
     <row r="192">
@@ -4823,16 +4823,16 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>50</v>
+        <v>205</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4</v>
+        <v>332</v>
       </c>
     </row>
     <row r="196">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="197">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>205</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>332</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5104,11 +5104,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205">
@@ -5122,16 +5122,16 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -5145,16 +5145,16 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5219,11 +5219,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="210">
@@ -5260,16 +5260,16 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>78</v>
+        <v>136</v>
       </c>
     </row>
     <row r="214">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="215">
@@ -7565,11 +7565,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>887</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>93</v>
+        <v>448</v>
       </c>
     </row>
     <row r="313">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>40</v>
+        <v>887</v>
       </c>
     </row>
     <row r="314">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>328</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315">
@@ -7657,11 +7657,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>448</v>
+        <v>328</v>
       </c>
     </row>
     <row r="316">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>5</v>
+        <v>291</v>
       </c>
     </row>
     <row r="317">
@@ -7703,11 +7703,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>44</v>
+        <v>189</v>
       </c>
     </row>
     <row r="318">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>189</v>
+        <v>44</v>
       </c>
     </row>
     <row r="319">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>291</v>
+        <v>30</v>
       </c>
     </row>
     <row r="321">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="322">
@@ -7818,11 +7818,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="323">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="325">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326">
@@ -7910,11 +7910,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>84</v>
+        <v>250</v>
       </c>
     </row>
     <row r="328">
@@ -7951,16 +7951,16 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>250</v>
+        <v>8614</v>
       </c>
     </row>
     <row r="329">
@@ -7974,16 +7974,16 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>8614</v>
+        <v>949</v>
       </c>
     </row>
     <row r="330">
@@ -8002,11 +8002,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>949</v>
+        <v>449</v>
       </c>
     </row>
     <row r="331">
@@ -8025,33 +8025,10 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
         <v>1925</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -458,11 +458,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2466</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1251</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -504,11 +504,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -550,11 +550,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>295</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -596,11 +596,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -642,11 +642,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>667</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
@@ -665,11 +665,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>429</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12">
@@ -711,11 +711,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -734,11 +734,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -821,16 +821,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6977</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="20">
@@ -1005,16 +1005,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1097,16 +1097,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1120,16 +1120,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
@@ -1143,16 +1143,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>319</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1212,16 +1212,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -1235,16 +1235,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>434</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38">
@@ -1286,11 +1286,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -1332,11 +1332,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1086</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41">
@@ -1350,16 +1350,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1483</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="43">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>778</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="44">
@@ -1419,16 +1419,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>483</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="45">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
@@ -1488,16 +1488,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
@@ -1557,16 +1557,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
@@ -1585,11 +1585,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1506</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>570</v>
+        <v>767</v>
       </c>
     </row>
     <row r="53">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>767</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="54">
@@ -1654,11 +1654,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>570</v>
       </c>
     </row>
     <row r="55">
@@ -1672,16 +1672,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4293</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="56">
@@ -1700,11 +1700,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>133</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -1718,16 +1718,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>46</v>
+        <v>409</v>
       </c>
     </row>
     <row r="58">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>409</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
@@ -1792,11 +1792,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1810,16 +1810,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>481</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
@@ -1833,16 +1833,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63">
@@ -1861,11 +1861,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -1884,11 +1884,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2339</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1793</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3764</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69">
@@ -1994,16 +1994,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>39337</v>
       </c>
     </row>
     <row r="70">
@@ -2017,16 +2017,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>470</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="71">
@@ -2040,16 +2040,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>39337</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="72">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>33828</v>
       </c>
     </row>
     <row r="73">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>237</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>33828</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="75">
@@ -2137,11 +2137,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>14014</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -2160,11 +2160,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>158968</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="77">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>37607</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="78">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>23323</v>
+        <v>176055</v>
       </c>
     </row>
     <row r="79">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>158968</v>
       </c>
     </row>
     <row r="80">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4144</v>
+        <v>37607</v>
       </c>
     </row>
     <row r="81">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>176055</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="82">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>15</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>276</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -2477,16 +2477,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
@@ -2505,11 +2505,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -2574,11 +2574,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>75</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>724</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5145</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -2707,16 +2707,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>22</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="101">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="102">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3219</v>
+        <v>724</v>
       </c>
     </row>
     <row r="103">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
@@ -2942,11 +2942,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>17855</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111">
@@ -2960,16 +2960,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>830</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>9</v>
+        <v>17855</v>
       </c>
     </row>
     <row r="113">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>285</v>
+        <v>830</v>
       </c>
     </row>
     <row r="116">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>147</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>287</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119">
@@ -3144,16 +3144,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="120">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>142</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1151</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3218,11 +3218,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>46</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>262</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>63</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="126">
@@ -3305,16 +3305,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1073</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>624</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="129">
@@ -3374,16 +3374,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1589</v>
+        <v>751</v>
       </c>
     </row>
     <row r="130">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>751</v>
+        <v>624</v>
       </c>
     </row>
     <row r="131">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135">
@@ -3535,16 +3535,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
@@ -3650,16 +3650,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
@@ -3724,11 +3724,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -3816,11 +3816,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154">
@@ -3954,11 +3954,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
@@ -4023,11 +4023,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158">
@@ -4041,16 +4041,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3346</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>916</v>
+        <v>807</v>
       </c>
     </row>
     <row r="161">
@@ -4110,16 +4110,16 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>807</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="162">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>75</v>
+        <v>916</v>
       </c>
     </row>
     <row r="163">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
@@ -4179,16 +4179,16 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
@@ -4230,11 +4230,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -4248,16 +4248,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>281</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168">
@@ -4271,16 +4271,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>281</v>
       </c>
     </row>
     <row r="169">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>148</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>148</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176">
@@ -4455,16 +4455,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
@@ -4501,16 +4501,16 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179">
@@ -4524,16 +4524,16 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="180">
@@ -4552,11 +4552,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="181">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>296</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="185">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="186">
@@ -4685,16 +4685,16 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>217</v>
+        <v>391</v>
       </c>
     </row>
     <row r="187">
@@ -4708,16 +4708,16 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>391</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
@@ -4759,11 +4759,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190">
@@ -4782,11 +4782,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191">
@@ -4800,16 +4800,16 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
     </row>
     <row r="192">
@@ -4823,16 +4823,16 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="193">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>205</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194">
@@ -4869,16 +4869,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>332</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
@@ -4966,11 +4966,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>22</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199">
@@ -4989,11 +4989,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5104,11 +5104,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
@@ -5122,16 +5122,16 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -5145,16 +5145,16 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
@@ -5196,11 +5196,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209">
@@ -5219,11 +5219,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="210">
@@ -5260,16 +5260,16 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>55</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>136</v>
+        <v>78</v>
       </c>
     </row>
     <row r="214">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -444,11 +444,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,66 +504,66 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>295</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>2071 - FAPEMIG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2466</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,20 +573,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,20 +596,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1011 - ALMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -619,20 +619,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>476</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -642,66 +642,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>429</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>1511 - PCMG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>667</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>861</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -711,20 +711,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -734,20 +734,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>529</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1021 - TCEMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -757,20 +757,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>217</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -780,20 +780,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -803,43 +803,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3765</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>4291 - FES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6977</v>
+        <v>8285</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -872,20 +872,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8557</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -895,20 +895,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1031 - TJMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -918,20 +918,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1161</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -941,20 +941,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -964,66 +964,66 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1441 - DEF PUB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,43 +1056,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1051 - TJMMG</t>
+          <t>1631 - SEC. GERAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1125,43 +1125,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1071 - GABINETE MILITAR</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1171,20 +1171,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>654</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1194,20 +1194,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1217,66 +1217,66 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>2321 - HEMOMINAS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>319</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1081 - AGE</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1286,20 +1286,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>434</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1336,39 +1336,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>778</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>483</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1378,20 +1378,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1365</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1401,43 +1401,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1086</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1091 - PGJ</t>
+          <t>2181 - FCS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1483</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1474,39 +1474,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2441 - ARSAE -MG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,20 +1516,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1539,20 +1539,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1101 - OGE</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1562,89 +1562,89 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>2041 - LEMG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>767</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4293</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1654,20 +1654,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>570</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1191 - SEF</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1677,20 +1677,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1700,43 +1700,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>2361 - IPLEMG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>409</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1746,20 +1746,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1221 - SEDE</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1792,20 +1792,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1815,66 +1815,66 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>481</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>1491 - SEGOV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1231 - SEAPA</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1884,20 +1884,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1907,20 +1907,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1930,20 +1930,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1953,20 +1953,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1976,66 +1976,66 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>190</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39337</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2301 - DER-MG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1793</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2045,20 +2045,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3764</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2068,43 +2068,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>33828</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>470</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1251 - PMMG</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2114,20 +2114,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2339</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2137,89 +2137,89 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2121 - IPSM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4144</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>1071 - GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>23323</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>176055</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2229,20 +2229,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>158968</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2252,20 +2252,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>37607</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14014</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2298,89 +2298,89 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>2311 - UNIMONTES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>157</v>
+        <v>538</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>276</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2390,20 +2390,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2413,20 +2413,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2436,20 +2436,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2459,43 +2459,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2505,66 +2505,66 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1301 - SEINFRA</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1051 - TJMMG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2574,43 +2574,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>21</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2620,20 +2620,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>333</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1371 - SEMAD</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>75</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2689,20 +2689,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>1031 - TJMG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2712,20 +2712,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>INATIVO MILITAR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3219</v>
+        <v>6858</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2735,20 +2735,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PRAÇA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1401 - CBMMG</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2758,20 +2758,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OFICIAL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>724</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2804,43 +2804,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>397</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>3151 - EMC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2850,20 +2850,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1441 - DEF PUB</t>
+          <t>2461 - ARMVA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2896,20 +2896,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>983</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2946,16 +2946,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>285</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,20 +2965,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NATUREZA ESPECIAL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>581</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2988,20 +2988,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>17855</v>
+        <v>988</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3011,16 +3011,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1139</v>
+        <v>749</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>804</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1451 - SEJUSP</t>
+          <t>2011 - IPSEMG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3061,16 +3061,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>830</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3103,20 +3103,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>142</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3130,39 +3130,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>142</v>
+        <v>17738</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1151</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3172,66 +3172,66 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>845</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1481 - SEDESE</t>
+          <t>1451 - SEJUSP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>147</v>
+        <v>895</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3241,20 +3241,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>262</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3264,43 +3264,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1721 - SCC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1073</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3310,20 +3310,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1491 - SEGOV</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3333,43 +3333,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1589</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3379,43 +3379,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>751</v>
+        <v>325</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1501 - SEPLAG</t>
+          <t>1081 - AGE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>624</v>
+        <v>203</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3425,43 +3425,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1067</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>7354</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1511 - PCMG</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3471,20 +3471,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10080</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3494,43 +3494,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19</v>
+        <v>283</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1371 - SEMAD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3540,20 +3540,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3563,43 +3563,43 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>135</v>
+        <v>290</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1521 - CGE</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>34</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3613,16 +3613,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3632,20 +3632,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3655,66 +3655,66 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1541 - ESP MG</t>
+          <t>1481 - SEDESE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3724,20 +3724,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3747,20 +3747,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3793,20 +3793,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1631 - SEC. GERAL</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3816,43 +3816,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>32</v>
+        <v>175</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>2351 - UEMG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>91</v>
+        <v>505</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3866,16 +3866,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>20</v>
+        <v>663</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1711 - SECOM</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3912,16 +3912,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>313</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3931,43 +3931,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>36</v>
+        <v>133</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>1501 - SEPLAG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3977,20 +3977,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1721 - SCC</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4000,20 +4000,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4023,20 +4023,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2241 - IGAM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>603</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2481 - DETRANMG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4092,43 +4092,43 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>807</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>2481 - DETRANMG</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3346</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2011 - IPSEMG</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4138,20 +4138,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>916</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4165,39 +4165,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>258</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>NATUREZA ESPECIAL</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4207,20 +4207,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>13</v>
+        <v>243</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2041 - LEMG</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4230,20 +4230,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4253,43 +4253,43 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>43</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>281</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4299,66 +4299,66 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>148</v>
+        <v>34165</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>57</v>
+        <v>874</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>1251 - PMMG</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>38749</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4368,20 +4368,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MEMBROS DE PODER</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2061 - FJP</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4391,20 +4391,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4414,20 +4414,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4441,62 +4441,62 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2071 - FAPEMIG</t>
+          <t>2331 - IPEMMG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4506,43 +4506,43 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>296</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4556,16 +4556,16 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4575,20 +4575,20 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2091 - FEAM</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4607,11 +4607,11 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4621,43 +4621,43 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>217</v>
+        <v>135</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>2201 - IEPHA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>266</v>
+        <v>65</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4667,43 +4667,43 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>262</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>391</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2101 - IEF</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4713,20 +4713,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OFICIAL</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>794</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4736,43 +4736,43 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>PRAÇA</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>1401 - CBMMG</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO MILITAR</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>36</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4782,20 +4782,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4805,43 +4805,43 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2121 - IPSM</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1521 - CGE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4855,16 +4855,16 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4874,20 +4874,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4897,20 +4897,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4</v>
+        <v>769</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>30</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4943,43 +4943,43 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>22</v>
+        <v>533</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1191 - SEF</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>205</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4989,20 +4989,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>332</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5012,20 +5012,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5035,43 +5035,43 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2161 - FUCAM</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5081,43 +5081,43 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>1231 - SEAPA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5127,43 +5127,43 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5173,20 +5173,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2171 - FAOP</t>
+          <t>3051 - EPAMIG</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5196,20 +5196,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>18</v>
+        <v>175</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5219,20 +5219,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5242,43 +5242,43 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>102</v>
+        <v>45</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5292,39 +5292,39 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>1301 - SEINFRA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2181 - FCS</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5338,39 +5338,39 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5407,16 +5407,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5430,16 +5430,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5449,43 +5449,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2201 - IEPHA</t>
+          <t>2251 - JUCEMG</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>22</v>
+        <v>124</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5495,20 +5495,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2281 - UTRAMIG</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5518,20 +5518,20 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5541,20 +5541,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2211 - TV MINAS</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5564,43 +5564,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>48</v>
+        <v>898</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5610,20 +5610,20 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5633,66 +5633,66 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>29</v>
+        <v>343</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>595</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2241 - IGAM</t>
+          <t>2371 - IMA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5702,43 +5702,43 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5752,16 +5752,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>103</v>
+        <v>224</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5771,20 +5771,20 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>25</v>
+        <v>282</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5798,39 +5798,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>13</v>
+        <v>183</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>2261 - FUNED</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3</v>
+        <v>276</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2251 - JUCEMG</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5840,43 +5840,43 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>274</v>
+        <v>946</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5886,20 +5886,20 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>202</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5909,20 +5909,20 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>284</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5932,20 +5932,20 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>26</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5955,43 +5955,43 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1091 - PGJ</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>829</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2261 - FUNED</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6001,43 +6001,43 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>239</v>
+        <v>33</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3772</v>
+        <v>75</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6051,16 +6051,16 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5571</v>
+        <v>364</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6074,16 +6074,16 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4222</v>
+        <v>534</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6093,20 +6093,20 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>633</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6120,16 +6120,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>291</v>
+        <v>24</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6139,66 +6139,66 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2271 - FHEMIG</t>
+          <t>1011 - ALMG</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4057</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6208,20 +6208,20 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>1711 - SECOM</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6263,11 +6263,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2281 - UTRAMIG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6277,43 +6277,43 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>2431 - AGÊNCIA RMBH</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5409</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6323,20 +6323,20 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>161</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>208</v>
+        <v>53</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6369,89 +6369,89 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2301 - DER-MG</t>
+          <t>1221 - SEDE</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>421</v>
+        <v>398</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>455</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6461,20 +6461,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1033</v>
+        <v>78</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6484,20 +6484,20 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6507,43 +6507,43 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1111</v>
+        <v>286</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2091 - FEAM</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2311 - UNIMONTES</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6553,43 +6553,43 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>379</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>223</v>
+        <v>613</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6599,20 +6599,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>281</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6622,20 +6622,20 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>65</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6645,20 +6645,20 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>722</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6668,43 +6668,43 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1</v>
+        <v>844</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2271 - FHEMIG</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>229</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2321 - HEMOMINAS</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6714,43 +6714,43 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>307</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6783,20 +6783,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>22</v>
+        <v>147</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -6815,11 +6815,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2331 - IPEMMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6829,20 +6829,20 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2061 - FJP</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6856,16 +6856,16 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>323</v>
+        <v>283</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6875,20 +6875,20 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>384</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6902,16 +6902,16 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>183</v>
+        <v>513</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>3041 - EMATER</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6944,20 +6944,20 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>7</v>
+        <v>863</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2351 - UEMG</t>
+          <t>2481 - DETRANMG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6967,20 +6967,20 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1696</v>
+        <v>149</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2481 - DETRANMG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6990,20 +6990,20 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -7022,11 +7022,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7036,20 +7036,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>217</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2361 - IPLEMG</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7059,89 +7059,89 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>10</v>
+        <v>227</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>585</v>
+        <v>296</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Mão De Obra Temporária</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>TERCEIRIZADO</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>909</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>2101 - IEF</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>34</v>
+        <v>411</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7151,20 +7151,20 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4</v>
+        <v>158</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2371 - IMA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7197,43 +7197,43 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,43 +7243,43 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>7</v>
+        <v>273</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7289,20 +7289,20 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,20 +7312,20 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,20 +7335,20 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2431 - AGÊNCIA RMBH</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,20 +7358,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,20 +7381,20 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>47</v>
+        <v>282</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2441 - ARSAE -MG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,43 +7404,43 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2461 - ARMVA</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7459,7 +7459,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -7473,16 +7473,16 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -7496,16 +7496,16 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -7519,20 +7519,20 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2471 - ARTEMIG</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,20 +7542,20 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,20 +7565,20 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7592,16 +7592,16 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>448</v>
+        <v>16</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7615,16 +7615,16 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>887</v>
+        <v>32</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -7643,57 +7643,57 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3041 - EMATER</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>328</v>
+        <v>32</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>1941 - EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>291</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7703,20 +7703,20 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>44</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3051 - EPAMIG</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7749,20 +7749,20 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>115</v>
+        <v>21486</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7772,20 +7772,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>30</v>
+        <v>14673</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,20 +7795,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>56</v>
+        <v>155811</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7818,218 +7818,34 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>16</v>
+        <v>39906</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3151 - EMC</t>
+          <t>1261 - SEE</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>3151 - EMC</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="E324" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>DIREÇÃO SUPERIOR</t>
-        </is>
-      </c>
-      <c r="E325" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="E327" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Inativo</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>INATIVO CIVIL</t>
-        </is>
-      </c>
-      <c r="E328" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>OUTRAS</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>4291 - FES</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>ESPECIALIZADA</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>1925</v>
+        <v>175450</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
+++ b/bancos/SISOR/BASE_CATEGORIA_PESSOAL.xlsx
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>158</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="295">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="296">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>38</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="297">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>OUTRAS</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="298">
@@ -7256,21 +7256,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>1271 - SECULT</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>MEMBROS DE PODER</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>273</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="299">
@@ -7279,21 +7279,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>4031 - FEPJ</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>7</v>
+        <v>6858</v>
       </c>
     </row>
     <row r="300">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7312,11 +7312,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>22</v>
+        <v>158</v>
       </c>
     </row>
     <row r="302">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7358,11 +7358,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="303">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>282</v>
+        <v>38</v>
       </c>
     </row>
     <row r="304">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>OUTRAS</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2151 - FHA</t>
+          <t>1271 - SECULT</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>53</v>
+        <v>273</v>
       </c>
     </row>
     <row r="306">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2471 - ARTEMIG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2471 - ARTEMIG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="308">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2471 - ARTEMIG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7496,11 +7496,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>TÉCNICA</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="309">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2471 - ARTEMIG</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7519,11 +7519,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="310">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7542,11 +7542,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>DIREÇÃO SUPERIOR</t>
+          <t>DOCENTE</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1</v>
+        <v>282</v>
       </c>
     </row>
     <row r="311">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7565,11 +7565,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DIREÇÃO E ASSESSORAMENTO</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>24</v>
+        <v>205</v>
       </c>
     </row>
     <row r="312">
@@ -7578,21 +7578,21 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2151 - FHA</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TÉCNICA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
     </row>
     <row r="313">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ESPECIALIZADA</t>
+          <t>DIREÇÃO SUPERIOR</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="315">
@@ -7647,21 +7647,21 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2421 - IDENE</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ESPECIALIZADA</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="316">
@@ -7670,21 +7670,21 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>1941 - EGE-SEPLAG</t>
+          <t>2471 - ARTEMIG</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>INATIVO CIVIL</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>1703</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>4125</v>
+        <v>24</v>
       </c>
     </row>
     <row r="319">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>21486</v>
+        <v>16</v>
       </c>
     </row>
     <row r="320">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>14673</v>
+        <v>32</v>
       </c>
     </row>
     <row r="321">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7795,11 +7795,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>DOCENTE</t>
+          <t>ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>155811</v>
+        <v>40</v>
       </c>
     </row>
     <row r="322">
@@ -7808,21 +7808,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>1261 - SEE</t>
+          <t>2421 - IDENE</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVA</t>
+          <t>INATIVO CIVIL</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>39906</v>
+        <v>32</v>
       </c>
     </row>
     <row r="323">
@@ -7831,20 +7831,296 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
+          <t>1941 - EGE-SEPLAG</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Inativo</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2161 - FUCAM</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2161 - FUCAM</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2161 - FUCAM</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2161 - FUCAM</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2161 - FUCAM</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Inativo</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>INATIVO CIVIL</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
           <t>1261 - SEE</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DIREÇÃO SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DIREÇÃO E ASSESSORAMENTO</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>21486</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADA</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>14673</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DOCENTE</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>155811</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>39906</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1261 - SEE</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
         <is>
           <t>Inativo</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>INATIVO CIVIL</t>
         </is>
       </c>
-      <c r="E323" t="n">
+      <c r="E335" t="n">
         <v>175450</v>
       </c>
     </row>
